--- a/Noticias_Calcario_20260728.xlsx
+++ b/Noticias_Calcario_20260728.xlsx
@@ -441,22 +441,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Distribuição de calcário a produtores rurais começa nesta semana em Santa Helena - Costa Oeste 93</t>
+          <t>Com guerra no Irã, estoque brasileiro de enxofre pode não alcançar setembro, afirma Ibram - Valor Econômico</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>28/07/2026 14:14</t>
+          <t>28/07/2026 15:39</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQNFFYRHBnbXpkWTlpb0ZIU2R3a1NyMDAyRWhmckxNbmJJeWpGbFNtT0s4OEFZSlg5X3hURTVERE5FekJMekQ4THY2ZGFMMzk2dXM1M1BxU3JLTTBQQkpZdFpWcVR3VkZyb2dVWVQ1WG9WcmM0Q3JkSy1TbUtNSGMyemptcGxnNUpJUENxYWNvSVhmSGktREdmYTg0NDdvMmY3d0NZcmhVTFpHRGU3UVlkbG02ZjBOYmdBRFloRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWHRWcEVlMmJVOEtOTFhYSUFrbkxvNVcxcTBXNXkwb3VFaXJ1NE5yMXNSZ3cxR0RPT1RhbGRLeTZvc3NFUGJHRDh1LTR5TU5YdXN3U0dtdVJTMElMUGlzUHJQeEVMVWhYbGVSa1BzQ2twNkxpZHZ0dUNVSjBBU1VYOTI1Vk9RUThBZ2xtbWJ4UGRBOHhNMk5Sc1M1QkR3Yk1MbHlSNGhvUU1CcjY2ZENpTTY2OW5yaGJra3pqXzc3ajE0SDZ2Vlczdk5weE54bjlsWml6ZWJwYl96QdIB6AFBVV95cUxQVENsWFVQaUIwTTNGaFItb2sxd1BoX2hLZ1cwTlpUYXJFUHVSd1RoUFFnMTFxR0sxTUJ5aHJVcXJyZXZ0NFpOcUEyTVRNOXlkWFA4ZVlyaW9TZ2JELTJpZ3owZ2k2QjE0SFIxS2wwVUxDWHRPb2s1cGNmTWhzWGxsUUxMbGlfcXlYWlFXakVxNWxkMzdGRkg1YUVfa3lnel9WQjFCUktvM1FoaUxBblVod013Y2dsX1ZPNk1Edkdpb3dkZDFmYlBQYmZza3pOQ3ZZRDVRQWlYR2tfSTFaNTJFd19IMGNlUWV3?oc=5</t>
         </is>
       </c>
     </row>
@@ -644,39 +644,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Crise global de enxofre afeta produção de fertilizantes e gera escassez no Brasil - G1</t>
+          <t>Antena 10 FM - Antena 10 FM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>27/07/2026 21:05</t>
+          <t>27/07/2026 21:17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPN1dLWTRLVFhnS0xxU0hTN21GZUd5SF8tWkFVd2pieVVQa2I2VDRhUFp6UWdwRHlQalh4c2h3OXZZekhuTGc1bmJFV01WNkt4eHVySk55SEw1VWR4aHFDcVcyQzlVS2NVdDJDU1lGekRIOG1hUHdZRkxoOWNhNDZWMEJFU3RNcUxEQ1dVLUIwVmdVdnlBMFBGTlFSWi1aUWNGWXplbGVXNVVDdWJfZThTajFjVm9CN05POGJURzR2QmwyQzNsT2l4VFNsb3M3UkRMcWd0TDgwMDRnMVnSAeoBQVVfeXFMTjUzNmZQamdjVlhkNmlETUNqanBRYS1Md2dFb3lWdkhYVFZwR0lYclREOENBR1l4Y3BpS2pPUDlBN1hzY1EzcUJYVkE5a19Ua0FwdDZYeWQ2aS02YXdxTzBsRGFDZzhwbkdHbTVVeVpiOFFpeHZGWTNOd3FnS1Q4Z2lnNkNqSDFKOEZQUnQwLUMxS2g4R0xVakRhaTVjWnFLYXJNLTFnWTZmZlFBRElDd19xRVhTaW9jT2lWc1NsbGxSdnZMckd4ZVE1TjdPWlRfbG1uWTRYZjZ0QzhjSXlSZDA0N1RBSjh3dU13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNT19DZV9aa196czB1LS1MSlJ2Y1V0RUY1NmNWR3lwZ3lmTE9pYTRoRnFidDRnUXFfMlhKWkpWQzF1U0l2OW5lYUcwMDNYSWpNNlZyLTc0eTRzN0dsdVQ0dE1NYVFGWTg3bmZMS2ctbXh3emY3RnRWb2p6YWxtQm50MHR0OTZYUDhBMTlJX3V5Zld1ZUMydjZyYUZwbHFsNVc3SkhDbW9pN3dCUHlvUUVseE1yY0hwYmM2TkNfamJxbDU1aWFvYWJSYXRn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Princípio de incêndio atinge rodotrem carregado com calcário na VRS-801 - lamais.com.br</t>
+          <t>Crise global de enxofre afeta produção de fertilizantes e gera escassez no Brasil - G1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>27/07/2026 20:07</t>
+          <t>27/07/2026 21:05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNSlExdUhPV0tReTZHRy0wT0RPeEVGZ044WFdKVGFEWmNwMWxkX2JDV2hlWU84T2RSTEYzODF2N2JTWUhUMzRJQXpqTExqUXRPbldJUWJyOHFxdUU0Rld4ZURaaGlGT0dLUDZDOXJPT29JcTdiT1lPSWNlT2RIdTh5d0w3UTVNSUpIblBnUlMxdmJ0cDl6WUJELThTS0FPYjgtNER6eEFtZWtGU1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPN1dLWTRLVFhnS0xxU0hTN21GZUd5SF8tWkFVd2pieVVQa2I2VDRhUFp6UWdwRHlQalh4c2h3OXZZekhuTGc1bmJFV01WNkt4eHVySk55SEw1VWR4aHFDcVcyQzlVS2NVdDJDU1lGekRIOG1hUHdZRkxoOWNhNDZWMEJFU3RNcUxEQ1dVLUIwVmdVdnlBMFBGTlFSWi1aUWNGWXplbGVXNVVDdWJfZThTajFjVm9CN05POGJURzR2QmwyQzNsT2l4VFNsb3M3UkRMcWd0TDgwMDRnMVnSAeoBQVVfeXFMTjUzNmZQamdjVlhkNmlETUNqanBRYS1Md2dFb3lWdkhYVFZwR0lYclREOENBR1l4Y3BpS2pPUDlBN1hzY1EzcUJYVkE5a19Ua0FwdDZYeWQ2aS02YXdxTzBsRGFDZzhwbkdHbTVVeVpiOFFpeHZGWTNOd3FnS1Q4Z2lnNkNqSDFKOEZQUnQwLUMxS2g4R0xVakRhaTVjWnFLYXJNLTFnWTZmZlFBRElDd19xRVhTaW9jT2lWc1NsbGxSdnZMckd4ZVE1TjdPWlRfbG1uWTRYZjZ0QzhjSXlSZDA0N1RBSjh3dU13?oc=5</t>
         </is>
       </c>
     </row>
@@ -1453,110 +1453,110 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Análise Técnica: Mosaic Co (MOS) — Suportes, Resistências e Indicadores - TradingKey</t>
+          <t>Muito antes do asfalto, romanos já preenchiam buracos com calcário, e uma obra na rodovia A1 encontrou os remendos preservados após cerca de 2 mil anos - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23/07/2026 04:00</t>
+          <t>22/07/2026 22:36</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9zRGdxQmcxSzVqLTNHMzVub1dXTmxKTDZEVlhZTlp1OXo4OGgySUI3SnVsTFpRTFdsUTlIMndrV0praU85dWdITEZBX2lmeXNHU0VqVXJ1bU5uOENISm0xVV9NYk9LXzNOQ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxQSURzMktZZVR0LVBwb1o5Y19ta1pmc2JuWkFqbGppdFpIX0txRlVZWE9OUFJDcjVlajQ2LXY5YW11bXF4cGpoZW5SRFpWSWx4OFhRTkhOSmhrZGE1Qm9zMWZaX2ZyVVBJd3c4eXp3dllFbS1faTlpNmVyMkxBREdTY1dWT1pfNDJNUXBGNmZqOWNuVGFQeGhaaFhFSjZzQU9GWklJbXl4MDBVR2Zkdllzc2JkY0JwT080WFY3RjlIMFRTN29WSWpkVHFuNkgxdmVDbUVnaUlTWm50TWxxcGdFanlKZHJjMUFUTlRnUHBlTG1TeEFVbGVIcUVpUEw1LUFJdTFITTNnbllRUWM2QklDVnBuelRqYnhJRUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Muito antes do asfalto, romanos já preenchiam buracos com calcário, e uma obra na rodovia A1 encontrou os remendos preservados após cerca de 2 mil anos - CPG Click Petróleo e Gás</t>
+          <t>Costa do Marfim: Banco Africano de Desenvolvimento concede um financiamento de 200 milhões de euros para reforçar a produção de combustíveis com baixo teor de enxofre - African Development Bank Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>22/07/2026 22:36</t>
+          <t>22/07/2026 16:19</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxQSURzMktZZVR0LVBwb1o5Y19ta1pmc2JuWkFqbGppdFpIX0txRlVZWE9OUFJDcjVlajQ2LXY5YW11bXF4cGpoZW5SRFpWSWx4OFhRTkhOSmhrZGE1Qm9zMWZaX2ZyVVBJd3c4eXp3dllFbS1faTlpNmVyMkxBREdTY1dWT1pfNDJNUXBGNmZqOWNuVGFQeGhaaFhFSjZzQU9GWklJbXl4MDBVR2Zkdllzc2JkY0JwT080WFY3RjlIMFRTN29WSWpkVHFuNkgxdmVDbUVnaUlTWm50TWxxcGdFanlKZHJjMUFUTlRnUHBlTG1TeEFVbGVIcUVpUEw1LUFJdTFITTNnbllRUWM2QklDVnBuelRqYnhJRUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wJBVV95cUxPZ3ltamlDUFg4Z0E1LW9Kak9Ic05rdTN5QmIxczBiR2NPaGctMnpjTEd3NnpmbFNscEdjS2dyUEcxVUlmcnpJbnRJd1YyS1lSTldxUVNYalc2eFpjdXVmcDNhWEVpNzM0cTZYTVZJenhLTzFaOUVZZjB3RzBIamg1cW1ma3BkSUNKNFlsV0ozajloVk9QQ3BNTVhOWVI5NExRXzNWYmhnU2p0QUpNMk5YSHFRbEhvbTE5UEstdktEU1p6UG04R1pqMmxZRHlGYklCc0hKcW9KVDZSamlUWEIyeVhsSEZaWDF3cFpoTjE0aG93RmFlT0VqUFVUNE1TOWNjTGh2ZU5CcXA2dDJmY01abkw0SVg3b0YwUm9CNGJHS2tzbDNKT0lEQV9wZU1nMXotbF9xQnp5cGU2Z3NHb1ctTE5faTcwX2dCenVCSWtTaUUtaFM0SWdZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Costa do Marfim: Banco Africano de Desenvolvimento concede um financiamento de 200 milhões de euros para reforçar a produção de combustíveis com baixo teor de enxofre - African Development Bank Group</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - MSN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>22/07/2026 16:19</t>
+          <t>22/07/2026 15:45</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wJBVV95cUxPZ3ltamlDUFg4Z0E1LW9Kak9Ic05rdTN5QmIxczBiR2NPaGctMnpjTEd3NnpmbFNscEdjS2dyUEcxVUlmcnpJbnRJd1YyS1lSTldxUVNYalc2eFpjdXVmcDNhWEVpNzM0cTZYTVZJenhLTzFaOUVZZjB3RzBIamg1cW1ma3BkSUNKNFlsV0ozajloVk9QQ3BNTVhOWVI5NExRXzNWYmhnU2p0QUpNMk5YSHFRbEhvbTE5UEstdktEU1p6UG04R1pqMmxZRHlGYklCc0hKcW9KVDZSamlUWEIyeVhsSEZaWDF3cFpoTjE0aG93RmFlT0VqUFVUNE1TOWNjTGh2ZU5CcXA2dDJmY01abkw0SVg3b0YwUm9CNGJHS2tzbDNKT0lEQV9wZU1nMXotbF9xQnp5cGU2Z3NHb1ctTE5faTcwX2dCenVCSWtTaUUtaFM0SWdZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiANBVV95cUxQVktma2phTTh1ZkRsdlRKNHh0MWd2QVpDYndvdUFEcjNMYXhycWlOZllpRW1mLTg5dmZHZVJQcU9iMHVlOEpibjBGenpELWpYczJLcFlDMFJyZlNYa3hPenpVX2VXOGJqWUxZQTJJY2ZxRjlaOTYwYmh4QUEyVWNHMktjWnJaVTJZR1J5T3RQS0dENmhaQjJnMDFPdUpscHNncXNqbHR6MFFRT0dVSmdxWjBwNGNnZy1UaWJjMGhVblV1RnpvUkxZWkY1aDZvUl95UGdZYjRERlV0NGlDa0VOcGl6a2hZeDV4SkJTU2ZLOUVUZDBMdThKOHhoMDdZNE9tclJyYXlfZjhoQmRhbFFEZ0tTSTl1NnQtVVNZZEZEM2JmSmNlZlg4M3gtejNoNC1JWUM2QUlETHNhLUxXalQ1Y2Y5ZEUtekp4Wi1oUWdaSW1uWmgwVG9mUUNra0tWaHZpSjFjN2JGMmFvcU11Y2FBbFBfWmRSdGFnY3FSVDdFMkhrNjRCaFREVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - MSN</t>
+          <t>Relação de preço da ureia e do milho no 1° semestre, entre 2018 e 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>22/07/2026 15:45</t>
+          <t>22/07/2026 15:01</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiANBVV95cUxQVktma2phTTh1ZkRsdlRKNHh0MWd2QVpDYndvdUFEcjNMYXhycWlOZllpRW1mLTg5dmZHZVJQcU9iMHVlOEpibjBGenpELWpYczJLcFlDMFJyZlNYa3hPenpVX2VXOGJqWUxZQTJJY2ZxRjlaOTYwYmh4QUEyVWNHMktjWnJaVTJZR1J5T3RQS0dENmhaQjJnMDFPdUpscHNncXNqbHR6MFFRT0dVSmdxWjBwNGNnZy1UaWJjMGhVblV1RnpvUkxZWkY1aDZvUl95UGdZYjRERlV0NGlDa0VOcGl6a2hZeDV4SkJTU2ZLOUVUZDBMdThKOHhoMDdZNE9tclJyYXlfZjhoQmRhbFFEZ0tTSTl1NnQtVVNZZEZEM2JmSmNlZlg4M3gtejNoNC1JWUM2QUlETHNhLUxXalQ1Y2Y5ZEUtekp4Wi1oUWdaSW1uWmgwVG9mUUNra0tWaHZpSjFjN2JGMmFvcU11Y2FBbFBfWmRSdGFnY3FSVDdFMkhrNjRCaFREVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPWlBYQkw2bl9fd3JLcG8wN3FvUkhLSHNYY1d6Um5COVM5RjNDUUZNSndYRzVQU2NXY3RodVl5bWx6aHRVcm0xeHEtWUx2SGNPYWZUYkgzVnR1akc0U1RXV3NMYmJYOERrQnhkLUYydW5RUkY4c1V5T0pOdzdldWZQZ1lNTk1iekVCTHJUUVlTbFd3dGgyUzFVR0ZBaXNpUmdabDhJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Relação de preço da ureia e do milho no 1° semestre, entre 2018 e 2026 - Farmnews</t>
+          <t>A nova joia da Mosaic custa mais de 20.000 € e apenas alguns poucos poderão comprá-la - brujulabike.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>22/07/2026 15:01</t>
+          <t>22/07/2026 14:35</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPWlBYQkw2bl9fd3JLcG8wN3FvUkhLSHNYY1d6Um5COVM5RjNDUUZNSndYRzVQU2NXY3RodVl5bWx6aHRVcm0xeHEtWUx2SGNPYWZUYkgzVnR1akc0U1RXV3NMYmJYOERrQnhkLUYydW5RUkY4c1V5T0pOdzdldWZQZ1lNTk1iekVCTHJUUVlTbFd3dGgyUzFVR0ZBaXNpUmdabDhJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNdmpIOTJoRUgwbF9JNlpCYXhDTEo2ZGp4aVpSTDNSNkVTWXViMzl5X2xfWmlaUmdkUzNJZnBSU2xjbDJtcmQ4SnJFY2dwOFI1QjREalNCQVQ0YlBUUFNZOS1Gem5xeFhCcjNsNGNyeS1yRG1FeWU0dDZzTVZTWVFDbm5GTEJ1MTBpaEFTeGx0QXFWaWxsOHE3YTc0a2JqUWN4QmM0N0wxRmF0RkY3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1568,17 +1568,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A nova joia da Mosaic custa mais de 20.000 € e apenas alguns poucos poderão comprá-la - brujulabike.com</t>
+          <t>Mosaic Biosciences and Elicit Plant Launch Joint Program to Develop New Canola Solutions for North America - AgriBusiness Global</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>22/07/2026 14:35</t>
+          <t>22/07/2026 11:32</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNdmpIOTJoRUgwbF9JNlpCYXhDTEo2ZGp4aVpSTDNSNkVTWXViMzl5X2xfWmlaUmdkUzNJZnBSU2xjbDJtcmQ4SnJFY2dwOFI1QjREalNCQVQ0YlBUUFNZOS1Gem5xeFhCcjNsNGNyeS1yRG1FeWU0dDZzTVZTWVFDbm5GTEJ1MTBpaEFTeGx0QXFWaWxsOHE3YTc0a2JqUWN4QmM0N0wxRmF0RkY3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQcGdBdWE2TFVpSEVWRGpzR05SdTVkTHF4TVVvTTBMRFVUMFhnNE5pRHR5VC1MYmNZMmhoQVpaaW9ELWFFRTktbE5yYkc5Ylp1ajRoQy1sd1g3QV9NZ0s4dENwaUxHOThZYy1VWjVUNThGeEItdFpBbU0xVWc2ZlMxQWtlOGdiMkFXWTVwUzNHVFF1RTNtOWNEcHljWEVJaFJMT2pZbGp1dGhaNms4bUw5UGE5ZmxRUHBUTnBHekZGNDZkdTZLb0x2MzBTdzk5ZVcxYWFWbFNvWjVJQkRzSGpxMU1KTzlhMXJJMGl5dXY2OFRxdl9waEhhRjVvSGljbTVpY1HSAYcCQVVfeXFMUE50d05SSzQ4VDFPdmlGV21qRmMyLWhrakkxUEZ3NS1qeVZFZVRNXzllbXIzMTNuY1B0eXFWa1RWR0hvZDVGYXA2aHp1YmstdHFXbzdHbWVOSkJ2aW1lQVFsd3RBTUxydFVNVEM0aDY0RmhCb0dmcEpBSmFpNy1vdVJpWWlLUVRlOFNjaW1aa0xXcHlCbXFfRzQwaHNUUE5xemJyWHZLcDlXZVJrR2VDOVRoWjk3dTg0T1UxOHp2YW9fc0ZnU2VlZGJHLWEwNExyYXVqZ3diMno1TDJtdEF2aHJ6UkJncWdKVGZNRjJIaHRKeWgtZlBOTHNyTmFoRXo1d2ttWXlQdTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1590,39 +1590,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mosaic Biosciences and Elicit Plant Launch Joint Program to Develop New Canola Solutions for North America - AgriBusiness Global</t>
+          <t>Escassez global de enxofre paralisa indústria de fertilizantes em Goiás e ameaça mais de 600 empregos - G1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>22/07/2026 11:32</t>
+          <t>22/07/2026 11:30</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQcGdBdWE2TFVpSEVWRGpzR05SdTVkTHF4TVVvTTBMRFVUMFhnNE5pRHR5VC1MYmNZMmhoQVpaaW9ELWFFRTktbE5yYkc5Ylp1ajRoQy1sd1g3QV9NZ0s4dENwaUxHOThZYy1VWjVUNThGeEItdFpBbU0xVWc2ZlMxQWtlOGdiMkFXWTVwUzNHVFF1RTNtOWNEcHljWEVJaFJMT2pZbGp1dGhaNms4bUw5UGE5ZmxRUHBUTnBHekZGNDZkdTZLb0x2MzBTdzk5ZVcxYWFWbFNvWjVJQkRzSGpxMU1KTzlhMXJJMGl5dXY2OFRxdl9waEhhRjVvSGljbTVpY1HSAYcCQVVfeXFMUE50d05SSzQ4VDFPdmlGV21qRmMyLWhrakkxUEZ3NS1qeVZFZVRNXzllbXIzMTNuY1B0eXFWa1RWR0hvZDVGYXA2aHp1YmstdHFXbzdHbWVOSkJ2aW1lQVFsd3RBTUxydFVNVEM0aDY0RmhCb0dmcEpBSmFpNy1vdVJpWWlLUVRlOFNjaW1aa0xXcHlCbXFfRzQwaHNUUE5xemJyWHZLcDlXZVJrR2VDOVRoWjk3dTg0T1UxOHp2YW9fc0ZnU2VlZGJHLWEwNExyYXVqZ3diMno1TDJtdEF2aHJ6UkJncWdKVGZNRjJIaHRKeWgtZlBOTHNyTmFoRXo1d2ttWXlQdTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQazVGaElwb0d2SFd0bjRwZE9yM2E3VEt3UzVZaV9TRUUtNGtsQ2tTS21jbVRNdXk0M3ZQd3Vhc3BtakpoN2JOZEh0UllpNFNNU1RBQVZLb0otVnN0cnRUMHNROTFVYWNzMDJ4bmNIbjhsaGhZZVFDcFllcV9oZ3dFa25HaWdtdDJWQ01jeEllTnRYYi0zMFhfMEJ3ekRuNl8xOTlUN2dWbGdkX1p3NnQ1N2FHbFRUWjJSUlNla3lTSFpFSlV6U2w3QVlrNW1OVm5HVjVtQllSaTN0d3ptWjdObnVSWUY2bDRWUGltadIB-wFBVV95cUxPallYVTZnVk1ndHB4SGlqWGVwUWxla2RjRlh3SWtrMy1hWFU4Zkk3czd0ejhral9ha3FKV3Y5Mk9YNDBmejdTVXc0eDZRdGdORDRENFRIZjdkQzhLTUl0Sl80Z1dRQm9HdGlRTGxDT19xTTV1OVZrbHlGWGV1ZUpEaEh6Z055NHZlTS1vblFhVWJuNm5VWGE2WE5KNElrdGJTbEdMSnJVWTVrMUNrNGE1NU9QaVAwRkwxYUtvMFh4Mm4wRzVPay1EdnVTUjZhV1J1Si1KSHYwYm9DcGVVdmZ1OHZNM3hicWttR21GV3BscHp6VlBpd2ljRTJZaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Escassez global de enxofre paralisa indústria de fertilizantes em Goiás e ameaça mais de 600 empregos - G1</t>
+          <t>Tensão no Oriente Médio pressiona ureia e petróleo - Revista Cultivar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>22/07/2026 11:30</t>
+          <t>22/07/2026 11:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQazVGaElwb0d2SFd0bjRwZE9yM2E3VEt3UzVZaV9TRUUtNGtsQ2tTS21jbVRNdXk0M3ZQd3Vhc3BtakpoN2JOZEh0UllpNFNNU1RBQVZLb0otVnN0cnRUMHNROTFVYWNzMDJ4bmNIbjhsaGhZZVFDcFllcV9oZ3dFa25HaWdtdDJWQ01jeEllTnRYYi0zMFhfMEJ3ekRuNl8xOTlUN2dWbGdkX1p3NnQ1N2FHbFRUWjJSUlNla3lTSFpFSlV6U2w3QVlrNW1OVm5HVjVtQllSaTN0d3ptWjdObnVSWUY2bDRWUGltadIB-wFBVV95cUxPallYVTZnVk1ndHB4SGlqWGVwUWxla2RjRlh3SWtrMy1hWFU4Zkk3czd0ejhral9ha3FKV3Y5Mk9YNDBmejdTVXc0eDZRdGdORDRENFRIZjdkQzhLTUl0Sl80Z1dRQm9HdGlRTGxDT19xTTV1OVZrbHlGWGV1ZUpEaEh6Z055NHZlTS1vblFhVWJuNm5VWGE2WE5KNElrdGJTbEdMSnJVWTVrMUNrNGE1NU9QaVAwRkwxYUtvMFh4Mm4wRzVPay1EdnVTUjZhV1J1Si1KSHYwYm9DcGVVdmZ1OHZNM3hicWttR21GV3BscHp6VlBpd2ljRTJZaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPYkR5djBjV3FhdGZkdUVIZG5oVzZEYnNJSGs4NHhuQ2l2emVzcURneEhJRC1NT0VIdkVpZlJqRGhfVUhTS0NWX0RjdnhWTTE4RXBYdGpnQUdSMmQ4bEh1MHJ1X0kzZVRNeXJmSENDMmRzSnVlWDZxZFRDb01TazkzQmZpMDh0WDF6SVFvbWJOZndza0dv?oc=5</t>
         </is>
       </c>
     </row>
@@ -1634,17 +1634,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tensão no Oriente Médio pressiona ureia e petróleo - Revista Cultivar</t>
+          <t>Pampa Energia anuncia investimentos de 2,7 Bilhões em fábrica de ureia na argentina - GlobalFert</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>22/07/2026 11:00</t>
+          <t>21/07/2026 20:18</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPYkR5djBjV3FhdGZkdUVIZG5oVzZEYnNJSGs4NHhuQ2l2emVzcURneEhJRC1NT0VIdkVpZlJqRGhfVUhTS0NWX0RjdnhWTTE4RXBYdGpnQUdSMmQ4bEh1MHJ1X0kzZVRNeXJmSENDMmRzSnVlWDZxZFRDb01TazkzQmZpMDh0WDF6SVFvbWJOZndza0dv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOcVVHZE43T3MwdHc2RUc0dWl0T3ExNFNMcGFraTJkeXRJZElYUzZmOXkwSkt5d09oRm92Y1BzU1VzdmN4bFBjRFVTUnRVU1BRTks2emRvWXh1Qm9VaDdTSVFNV2p5TWNpaXZaZVlmRFZCYXF2c0YxZFU3blhrVVB5VUxHOVdkbkl0Q0lVak1MeHRjWjdDeVlCc0Fwd3IyakgwczdXczFLRmRDNUJPR2p3bHRjSlBPd1VTVHZWMGxaNWRTTktoWGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1656,39 +1656,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pampa Energia anuncia investimentos de 2,7 Bilhões em fábrica de ureia na argentina - GlobalFert</t>
+          <t>Fertilizantes e açúcar entram em alerta: alta da ureia, queda na moagem e riscos globais elevam incertezas para o agronegócio - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>21/07/2026 20:18</t>
+          <t>21/07/2026 18:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOcVVHZE43T3MwdHc2RUc0dWl0T3ExNFNMcGFraTJkeXRJZElYUzZmOXkwSkt5d09oRm92Y1BzU1VzdmN4bFBjRFVTUnRVU1BRTks2emRvWXh1Qm9VaDdTSVFNV2p5TWNpaXZaZVlmRFZCYXF2c0YxZFU3blhrVVB5VUxHOVdkbkl0Q0lVak1MeHRjWjdDeVlCc0Fwd3IyakgwczdXczFLRmRDNUJPR2p3bHRjSlBPd1VTVHZWMGxaNWRTTktoWGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwJBVV95cUxOOTNTZ3BvRFJVWUlfNzVjb0dlT2JOelNkUUQwb3JvSGlBWUpvcFdnVTBaLUhjem9yUmc3eVVpN3VOY2tXVEw1UTN3aDRpZjlqb3FWSEVMVFVvUU5BTWswM25QT0hseGJYOUpBMHM4amQ5emZfM3MtUGtwM1BTSFZYaWM5NldDR3lPYzVkUmplTTRaSXlrQ19vTXJZSXFISnNoOXVSS3k2blZRQnpnY29Va1Awc0JZSTZxbjRRVzRsbzhTQ0xjV21vM0trUkRxNG5zZHYtdGhxSHBOQkg2ZERndmtPcWNxNVJnT1ZQWHJjVG82bF8tU194QlVPaWRSbVgtb1RPalVwdk00Z2o4bzMwYlQtbkVZT2tMSzhoRFo1c0djNkwxZ0pXUUhicw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fertilizantes e açúcar entram em alerta: alta da ureia, queda na moagem e riscos globais elevam incertezas para o agronegócio - Portal do Agronegócio</t>
+          <t>Mosaic pode demitir mais 650 funcionários em Catalão por causa da falta de matéria-prima provocada pela guerra no Irã - O Popular</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>21/07/2026 18:00</t>
+          <t>21/07/2026 17:19</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwJBVV95cUxOOTNTZ3BvRFJVWUlfNzVjb0dlT2JOelNkUUQwb3JvSGlBWUpvcFdnVTBaLUhjem9yUmc3eVVpN3VOY2tXVEw1UTN3aDRpZjlqb3FWSEVMVFVvUU5BTWswM25QT0hseGJYOUpBMHM4amQ5emZfM3MtUGtwM1BTSFZYaWM5NldDR3lPYzVkUmplTTRaSXlrQ19vTXJZSXFISnNoOXVSS3k2blZRQnpnY29Va1Awc0JZSTZxbjRRVzRsbzhTQ0xjV21vM0trUkRxNG5zZHYtdGhxSHBOQkg2ZERndmtPcWNxNVJnT1ZQWHJjVG82bF8tU194QlVPaWRSbVgtb1RPalVwdk00Z2o4bzMwYlQtbkVZT2tMSzhoRFo1c0djNkwxZ0pXUUhicw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOUHB5NHZZVzBfMXAxUUMxNUF2U2QxdVVJYnlXdzE4alNEbU5nRmxoRnhvSzR2WWs4RmF1ZXZOd1pTRmVTeU1iQ1A0QzZ6RjZSZnZlMUNxV0xaOGkycEM5clZrSVNYU2VDMWVYeU1IX0Fid0t5c2xjYnlkM1ZtR2pQOFhLcWV6dkhLckhYcmFQSFByZzlabmV3aWcwVWpEYTQ1Vm04VFRpQjlBMXRYb2hxUkRmSEdfd2poNXhHaUFZbGZfdVoyVEVQWktLRkh6RzhUcFotN0ZGVEcxRi1lQ01meEN6WHZxY0N3Qzd0UFBra00?oc=5</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mosaic pode demitir mais 650 funcionários em Catalão por causa da falta de matéria-prima provocada pela guerra no Irã - O Popular</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - GC Notícias</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>21/07/2026 17:19</t>
+          <t>21/07/2026 14:56</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOUHB5NHZZVzBfMXAxUUMxNUF2U2QxdVVJYnlXdzE4alNEbU5nRmxoRnhvSzR2WWs4RmF1ZXZOd1pTRmVTeU1iQ1A0QzZ6RjZSZnZlMUNxV0xaOGkycEM5clZrSVNYU2VDMWVYeU1IX0Fid0t5c2xjYnlkM1ZtR2pQOFhLcWV6dkhLckhYcmFQSFByZzlabmV3aWcwVWpEYTQ1Vm04VFRpQjlBMXRYb2hxUkRmSEdfd2poNXhHaUFZbGZfdVoyVEVQWktLRkh6RzhUcFotN0ZGVEcxRi1lQ01meEN6WHZxY0N3Qzd0UFBra00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOYzhEZ3kwNU5UX2toZW5MenhVQ1p4V0xkUXlUeVloSWV4SGFFaTY2NGZfRnFWYXR3cVlFTWFwTmdDTlFwRkpTemRpcnpXLVFuOW5OVWhKUm1LUUFnWHpFNjFxdzctT0JyRVU3R0ktU2tybC1aeU1XTzItdDlETTA0cTV5RVllQlN2eUFPQTV6dGFEZkFlZUlRX1h4YmN0WTEtenItQkRDOTV5dHdFY2RLaEFkb25ZMWZzV05FcEdLaFhmQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1722,17 +1722,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - GC Notícias</t>
+          <t>Crise na Mosaic: Sindicato Metabase cobra complementação salarial para trabalhadores de Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>21/07/2026 14:56</t>
+          <t>21/07/2026 13:58</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOYzhEZ3kwNU5UX2toZW5MenhVQ1p4V0xkUXlUeVloSWV4SGFFaTY2NGZfRnFWYXR3cVlFTWFwTmdDTlFwRkpTemRpcnpXLVFuOW5OVWhKUm1LUUFnWHpFNjFxdzctT0JyRVU3R0ktU2tybC1aeU1XTzItdDlETTA0cTV5RVllQlN2eUFPQTV6dGFEZkFlZUlRX1h4YmN0WTEtenItQkRDOTV5dHdFY2RLaEFkb25ZMWZzV05FcEdLaFhmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBZWGNlWl9BREdTckFNcWVybVhfbXI4R3NvX3JuM2NCbWhrNVpMdElFTlQxNlhaV0VNZFdZM2FRWDI0VkZYWlpaRlBlbWJycjl5bVlLWlNBTnd3X1ZmMjRDOUNxRFFPdEpabnU3UXhNeVB6eHZBeEHSAcACQVVfeXFMTkJ6YkEtcVNlcVhFYTlXbGxEcFNMUVgxaTFvMHZLamh6M0Y0LThPcVdfSTE2aHhfcTZENl9UVUdmUGR2SkhwS0NYZ19rbWJfMlBSWXVHd2NvY1NHUFdHaFNlVlVnejlKN3U0LTZsdFBfY1NzdTN6Yms3S1Q3bk5Zb2JwUEo0RVIzSjB3YnpnRVZEVWRwYUt5Vml2ZEdyMFpMLU5DNzdYay1BcVZTbnhaZnNoSkpDY3d4eHhQbHlkSDlhb0hzcFdhd2VIWXNkUGt0aDFlSmhkakFwNlhXTm51Z2NZRUZ4VGRTNkZUZFNpc2hzZmVOZXMzOC1fM3ZXUXdwWEFuZTVaOElLRzExTklCYVRxSWNMZkNVR2ZQZ3BTZjlGY3lvZ0M1UnBZemR4Y2JyWGQ3d2prT1VuUDBpSktXNG4?oc=5</t>
         </is>
       </c>
     </row>
@@ -1744,127 +1744,127 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Crise na Mosaic: Sindicato Metabase cobra complementação salarial para trabalhadores de Catalão - Badiinho</t>
+          <t>Mercado internacional pressiona setor de fertilizantes e afeta unidade da Mosaic em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>21/07/2026 13:58</t>
+          <t>21/07/2026 12:53</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBZWGNlWl9BREdTckFNcWVybVhfbXI4R3NvX3JuM2NCbWhrNVpMdElFTlQxNlhaV0VNZFdZM2FRWDI0VkZYWlpaRlBlbWJycjl5bVlLWlNBTnd3X1ZmMjRDOUNxRFFPdEpabnU3UXhNeVB6eHZBeEHSAcACQVVfeXFMTkJ6YkEtcVNlcVhFYTlXbGxEcFNMUVgxaTFvMHZLamh6M0Y0LThPcVdfSTE2aHhfcTZENl9UVUdmUGR2SkhwS0NYZ19rbWJfMlBSWXVHd2NvY1NHUFdHaFNlVlVnejlKN3U0LTZsdFBfY1NzdTN6Yms3S1Q3bk5Zb2JwUEo0RVIzSjB3YnpnRVZEVWRwYUt5Vml2ZEdyMFpMLU5DNzdYay1BcVZTbnhaZnNoSkpDY3d4eHhQbHlkSDlhb0hzcFdhd2VIWXNkUGt0aDFlSmhkakFwNlhXTm51Z2NZRUZ4VGRTNkZUZFNpc2hzZmVOZXMzOC1fM3ZXUXdwWEFuZTVaOElLRzExTklCYVRxSWNMZkNVR2ZQZ3BTZjlGY3lvZ0M1UnBZemR4Y2JyWGQ3d2prT1VuUDBpSktXNG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9sQ2F2MExzRmNzdndHMHMzblNRNHNaaXg5NDY2NXpCbkFuY24weFZpNEtXTFgzeHZzMzFrWTlVR2pkSllSdkpHR0xNNzZYbURHZ2FYRDBxcHJDMTRfTVpMZlZmZWdLcWPSAWxBVV95cUxPY2U5czZRTjNZRzNEVlBRS1ZKTlVYTDFuUjFJRFRLUXBXVExqZUkwXzZBb0FYX29qT0EydzZBMzFjSzJINWliWEFrR3ByNHdWZDNGRlROelRLX2k3M3RyTVc3T3BxWFAwUVhsLUI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mercado internacional pressiona setor de fertilizantes e afeta unidade da Mosaic em Catalão - Badiinho</t>
+          <t>Parceria entre Sindicato de Produtores Rurais de Bragança (PA) e Prefeitura fortalece a agricultura com entrega de calcário e acesso a políticas públicas - Portal CNA Brasil</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>21/07/2026 12:53</t>
+          <t>21/07/2026 10:31</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9sQ2F2MExzRmNzdndHMHMzblNRNHNaaXg5NDY2NXpCbkFuY24weFZpNEtXTFgzeHZzMzFrWTlVR2pkSllSdkpHR0xNNzZYbURHZ2FYRDBxcHJDMTRfTVpMZlZmZWdLcWPSAWxBVV95cUxPY2U5czZRTjNZRzNEVlBRS1ZKTlVYTDFuUjFJRFRLUXBXVExqZUkwXzZBb0FYX29qT0EydzZBMzFjSzJINWliWEFrR3ByNHdWZDNGRlROelRLX2k3M3RyTVc3T3BxWFAwUVhsLUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxQQllOWWdoRGR5V2xNN2tPakpEcHRwY3BLVFhiUS1nM0h2TFlhUDBqYVk2a0NqYnd4VlpaSktsYzBGV0tQTS1wTE9wam93clY0c0hQUjNIdFgyS3djYnlHMzI0YlRFRGs3MWkxYTg0cGJYZGdWcG02X1BaS1Z0QUlJdGMzY2RjcXRxTk1idS1rcUNzRGh6VmpyMFJvYlBUbDJSVGFROEZUQmt3ZXdTdWFTZ3hUTUxuUkx3TGpOSkFPRHhRYkFQdHNRWldHaWc0OXZwSlhtUnUtcXRTdzNyc0Utd0RyUEVsVDlHU3R4NnBROFFtUk02dW9RUFl0SWJxS1VuaHctT2lmUTdzdmZQVWtNZm5Eaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Parceria entre Sindicato de Produtores Rurais de Bragança (PA) e Prefeitura fortalece a agricultura com entrega de calcário e acesso a políticas públicas - Portal CNA Brasil</t>
+          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>21/07/2026 10:31</t>
+          <t>21/07/2026 06:09</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxQQllOWWdoRGR5V2xNN2tPakpEcHRwY3BLVFhiUS1nM0h2TFlhUDBqYVk2a0NqYnd4VlpaSktsYzBGV0tQTS1wTE9wam93clY0c0hQUjNIdFgyS3djYnlHMzI0YlRFRGs3MWkxYTg0cGJYZGdWcG02X1BaS1Z0QUlJdGMzY2RjcXRxTk1idS1rcUNzRGh6VmpyMFJvYlBUbDJSVGFROEZUQmt3ZXdTdWFTZ3hUTUxuUkx3TGpOSkFPRHhRYkFQdHNRWldHaWc0OXZwSlhtUnUtcXRTdzNyc0Utd0RyUEVsVDlHU3R4NnBROFFtUk02dW9RUFl0SWJxS1VuaHctT2lmUTdzdmZQVWtNZm5Eaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQU0xaTWc1c2EwcWlLbXJ6OVpBWDZyOXc0b3hMQjYyOEpNUVFpSHpQU0FONUJLa0dHUDFQc3RPaVlkZ1BZUWNuZlk5eC1mcmUwWEY3dXV2NVNmRjZza0lMU2xZMmRtQ0FBOEpOWEV1a1lFR3FZTWpEaFZNUGhOazVUN2kyT2tYVThuR3NUZ2RlSUNBYlZXeHd2ODJUTEI5UExqT05kalMza0lDQXB0eXJmT1FR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - brasilagro.com.br</t>
+          <t>Galeria de Limestone, Granite and Travertine - 6 - ArchDaily</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>21/07/2026 06:09</t>
+          <t>21/07/2026 05:23</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQU0xaTWc1c2EwcWlLbXJ6OVpBWDZyOXc0b3hMQjYyOEpNUVFpSHpQU0FONUJLa0dHUDFQc3RPaVlkZ1BZUWNuZlk5eC1mcmUwWEY3dXV2NVNmRjZza0lMU2xZMmRtQ0FBOEpOWEV1a1lFR3FZTWpEaFZNUGhOazVUN2kyT2tYVThuR3NUZ2RlSUNBYlZXeHd2ODJUTEI5UExqT05kalMza0lDQXB0eXJmT1FR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNX2VUbDl2MmQzNHVXM2l2NHByYVc1ZldveGJaMWNJRlEzaVNRTnh6b2l0OWJFTnJmTjY5X2VpWU1rYXR3RGN6bGRubldjTTJWckVUVk85WVFCN3QyTXdKT2xrNnBSSEFHaUJPbUFSeTFYcWFjc2ZMdmRhdEFabEEyYXU0RFV2cm8xYXBtMmFadW92aXFzLWw5SHFiWGJhUUh5TzlzV0E1WVpiR05vcnVfRlFFbDdlWDljeW5vYzUyTnp6ZkFhamNKcGxWa09MaHMtU28yZ3FDaG5KVV9ZSEJoQ1FaZXlMbWpJak1VMWN0TQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Galeria de Limestone, Granite and Travertine - 6 - ArchDaily</t>
+          <t>Com “brisa de otimismo”, mercado de fertilizantes reage, mas ainda corre contra o tempo - AgFeed</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>21/07/2026 05:23</t>
+          <t>20/07/2026 18:27</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNX2VUbDl2MmQzNHVXM2l2NHByYVc1ZldveGJaMWNJRlEzaVNRTnh6b2l0OWJFTnJmTjY5X2VpWU1rYXR3RGN6bGRubldjTTJWckVUVk85WVFCN3QyTXdKT2xrNnBSSEFHaUJPbUFSeTFYcWFjc2ZMdmRhdEFabEEyYXU0RFV2cm8xYXBtMmFadW92aXFzLWw5SHFiWGJhUUh5TzlzV0E1WVpiR05vcnVfRlFFbDdlWDljeW5vYzUyTnp6ZkFhamNKcGxWa09MaHMtU28yZ3FDaG5KVV9ZSEJoQ1FaZXlMbWpJak1VMWN0TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVVh2bHF6bEVibGowdkxud1piX1FVWEpHWTVpLXNWUW80eU92UXVUdElvOFlJMEVRaDcwckhLZmtQcmJnOElrU1RlSEhKeEZzRjRzRmJHZW1Cb3BqOG9KR2FoeTZQNVM1b1l4aUZvVmhCeTBfQ2Q1ZndnbEFOLUkwQ1YwYXd3ZGw0cExzR2w5bVNsNG9zODh1bkVad2pZdFpodmdEbFVIcGtYSnlHLTU2S1hQem92QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Com “brisa de otimismo”, mercado de fertilizantes reage, mas ainda corre contra o tempo - AgFeed</t>
+          <t>Pampa Energía confirma nova fábrica de ureia de US$ 2,7 bi que mira o Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>20/07/2026 18:27</t>
+          <t>20/07/2026 17:29</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVVh2bHF6bEVibGowdkxud1piX1FVWEpHWTVpLXNWUW80eU92UXVUdElvOFlJMEVRaDcwckhLZmtQcmJnOElrU1RlSEhKeEZzRjRzRmJHZW1Cb3BqOG9KR2FoeTZQNVM1b1l4aUZvVmhCeTBfQ2Q1ZndnbEFOLUkwQ1YwYXd3ZGw0cExzR2w5bVNsNG9zODh1bkVad2pZdFpodmdEbFVIcGtYSnlHLTU2S1hQem92QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeFZEM0NBMDFsS3ZfN1VJTDE1ZjJ3bGZMcG9qVUgtNjhWb0VxODFEUHhkRHFJZ2w0RmZEbDJSNFI5VXV2OE5IR1RRTTZWVXZSUVg1SFBmbXRxYkl6czNqWU1BRS1LWFROQUJlcjdybEQ3SmFDb0NKMDk2ZFkxb193NzFuOGh0YTJJUUtrTmR1MmotcGNZSDBJdDZRdDNEOVpaQ1lSU0duRm1BblF2NFB3aWZqR1dnb1EyRWp0X1NnVVp2TC1fcjNtenVB0gHYAUFVX3lxTE1rRjEwOVdRaURTMDIyNnpHR09ydml4SnlSdVl3MnFBOHMxR0RsMUxGYzNMMjVBYzJ2OVRuWG1HbjNMRnRfZzRmSUUxbzgzcHJacFNSWXdIemdxd3daSDBMWnQ5OHc4OUJRN2kzdW02X19xeWpPRUREc2taYkY0RmNCUkRlYnRuVG9vdkFnNUEzYlUwR3FtR2MyWVFJOVRBYzktcTVCdVZGM3FYUVVyd0FrYzJwb3lvcjJvc2M0cWJaMG51VERCVHlNNXVjc3lnOFJ2aFg0VHBmbQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1876,17 +1876,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pampa Energía confirma nova fábrica de ureia de US$ 2,7 bi que mira o Brasil - Valor Econômico</t>
+          <t>Tensão geopolítica impulsiona alta da ureia, avalia StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>20/07/2026 17:29</t>
+          <t>20/07/2026 17:06</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeFZEM0NBMDFsS3ZfN1VJTDE1ZjJ3bGZMcG9qVUgtNjhWb0VxODFEUHhkRHFJZ2w0RmZEbDJSNFI5VXV2OE5IR1RRTTZWVXZSUVg1SFBmbXRxYkl6czNqWU1BRS1LWFROQUJlcjdybEQ3SmFDb0NKMDk2ZFkxb193NzFuOGh0YTJJUUtrTmR1MmotcGNZSDBJdDZRdDNEOVpaQ1lSU0duRm1BblF2NFB3aWZqR1dnb1EyRWp0X1NnVVp2TC1fcjNtenVB0gHYAUFVX3lxTE1rRjEwOVdRaURTMDIyNnpHR09ydml4SnlSdVl3MnFBOHMxR0RsMUxGYzNMMjVBYzJ2OVRuWG1HbjNMRnRfZzRmSUUxbzgzcHJacFNSWXdIemdxd3daSDBMWnQ5OHc4OUJRN2kzdW02X19xeWpPRUREc2taYkY0RmNCUkRlYnRuVG9vdkFnNUEzYlUwR3FtR2MyWVFJOVRBYzktcTVCdVZGM3FYUVVyd0FrYzJwb3lvcjJvc2M0cWJaMG51VERCVHlNNXVjc3lnOFJ2aFg0VHBmbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPRTFaSlhVS2VHUElxU1duN3ZDRVRYYWcweWN4MG1nY1RUYWQ4bkVmeFQ0Tld6RW9jZWJOSmFVOFUwdFJpWVFRelF0WVV1ZGIwczYycWpxN1VvdkJzSGhyd1doYm52bF9FVVoxQ0hhcGRlT3h3bHpwVGVBNWNfTDlDQWxQd0V4WHNRemNDT2o0eXh4X3V0TF8zNGtyS3NuUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1898,17 +1898,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tensão geopolítica impulsiona alta da ureia, avalia StoneX - Revista Cultivar</t>
+          <t>Cotações da ureia voltam a ganhar força e acumulam três semanas de alta - Globo Rural</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>20/07/2026 17:06</t>
+          <t>20/07/2026 16:28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPRTFaSlhVS2VHUElxU1duN3ZDRVRYYWcweWN4MG1nY1RUYWQ4bkVmeFQ0Tld6RW9jZWJOSmFVOFUwdFJpWVFRelF0WVV1ZGIwczYycWpxN1VvdkJzSGhyd1doYm52bF9FVVoxQ0hhcGRlT3h3bHpwVGVBNWNfTDlDQWxQd0V4WHNRemNDT2o0eXh4X3V0TF8zNGtyS3NuUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPNE43X3FKaDhjVWxiYmRWTGNFb2kyU0hka3lSbzVjQllEVXBmRVh6N3UxdVREQlREYS1fb2wzNTNjcF9BRnI1QU1ZX0VBSDBKRWp1SXo4dkU5ZFdreHJJNVZ4bTNOM1V3ZjJieTFxQnpQSm9wWTJjUmlpU3Y0YXhlamItUmx4MnZuckNBTF8xbWtvQ25VWGo4dVdST1JhS2tWR0MtNHY2XzQ4d1ByUHo1ak5BS0xrZFRRaUlpbWFERnNXV29PS1VLMzNR0gHYAUFVX3lxTE5FeHdzOEpTZzVPeWhxeEhIbGlQMVJiejdsMGlxRnlDcU1vSDhhcXJTcGVDWmtqc0NsTXUwWGhtVzNhLXNZbFhncWc3cWhJZWxaUFpJZ21DTkNZT3p3eVR2aUEzcEFVUkZ4S0QwbEwydmJ6R2tVX2tVUWtXVm1VbVgwX2Y0TkQ5cFB0WWduTWZxcVJwOHc5SzJXSi1PWnV5QUt0LWI4X1ZpVlh2UUo0Zm5udWhzYTl1MXRxOWtwZ1cwVmJUUVRTZFpGc0dmQ0VHZUtKeVFsUjFBNQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1920,61 +1920,61 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cotações da ureia voltam a ganhar força e acumulam três semanas de alta - Globo Rural</t>
+          <t>Ureia sobe com retomada da demanda e tensões no Oriente Médio - StoneX</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>20/07/2026 16:28</t>
+          <t>20/07/2026 14:55</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPNE43X3FKaDhjVWxiYmRWTGNFb2kyU0hka3lSbzVjQllEVXBmRVh6N3UxdVREQlREYS1fb2wzNTNjcF9BRnI1QU1ZX0VBSDBKRWp1SXo4dkU5ZFdreHJJNVZ4bTNOM1V3ZjJieTFxQnpQSm9wWTJjUmlpU3Y0YXhlamItUmx4MnZuckNBTF8xbWtvQ25VWGo4dVdST1JhS2tWR0MtNHY2XzQ4d1ByUHo1ak5BS0xrZFRRaUlpbWFERnNXV29PS1VLMzNR0gHYAUFVX3lxTE5FeHdzOEpTZzVPeWhxeEhIbGlQMVJiejdsMGlxRnlDcU1vSDhhcXJTcGVDWmtqc0NsTXUwWGhtVzNhLXNZbFhncWc3cWhJZWxaUFpJZ21DTkNZT3p3eVR2aUEzcEFVUkZ4S0QwbEwydmJ6R2tVX2tVUWtXVm1VbVgwX2Y0TkQ5cFB0WWduTWZxcVJwOHc5SzJXSi1PWnV5QUt0LWI4X1ZpVlh2UUo0Zm5udWhzYTl1MXRxOWtwZ1cwVmJUUVRTZFpGc0dmQ0VHZUtKeVFsUjFBNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPdVlYMDZsdXIycGJycGFsS2lBVlliVThkYVZNRi1qSUlmRjZQeG1XN05Fc0JvcHB0QmtOVmV4WEhGbk51OWFyODZqblZwXzVOMlBuUWJjSHZtUDZxeUtyT2VBUmgxSjRxanRUNnRaSmJhQ2RoUjdlYmhjWC00Njl1LXItczhoMWd4ZkFFUlJMVVdWZG1WdE04Y240RV9HRlcyMGNybDJZQXBlUHpkU3Z0Zjg4b3ZuanVROVdnaGxLcUtTZFZiQXUwZS05Mm13MkNCdG1HSHpEdWtDOUVWNW01TGI3UEdIdGxwRmg1aEowZThtTVdKUGdoUV81THVLRG9kcUozR2MzWFk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ureia sobe com retomada da demanda e tensões no Oriente Médio - StoneX</t>
+          <t>Escassez de enxofre fecha fábricas, ameaça oferta de adubo e pressiona custos do agronegócio brasileiro - JBNEWS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>20/07/2026 14:55</t>
+          <t>20/07/2026 13:41</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPdVlYMDZsdXIycGJycGFsS2lBVlliVThkYVZNRi1qSUlmRjZQeG1XN05Fc0JvcHB0QmtOVmV4WEhGbk51OWFyODZqblZwXzVOMlBuUWJjSHZtUDZxeUtyT2VBUmgxSjRxanRUNnRaSmJhQ2RoUjdlYmhjWC00Njl1LXItczhoMWd4ZkFFUlJMVVdWZG1WdE04Y240RV9HRlcyMGNybDJZQXBlUHpkU3Z0Zjg4b3ZuanVROVdnaGxLcUtTZFZiQXUwZS05Mm13MkNCdG1HSHpEdWtDOUVWNW01TGI3UEdIdGxwRmg1aEowZThtTVdKUGdoUV81THVLRG9kcUozR2MzWFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQa3FIWUJOeFVabjdUd3VBS2FRV29fQlpNaURDU3ZpdlB2b2UwNnpreFF5aFg1Z3g4TmM0bmRmZkJRNHUyTjg5dFhZLTVDMEE2b3RHdi16aUJnVUpnYVlodEVFRUg0b3lYUFVwU1lNVy1sX1lreVJ4WnRLOG1SODVuUW95ZkZyQm5WOXhPNXF1VTR5S21DVEdJZ3dZWVVETFNESlRBTVZyd1NDNEhXbzN6cXdha2RISVhIVVJSeS1peWNRZlk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Escassez de enxofre fecha fábricas, ameaça oferta de adubo e pressiona custos do agronegócio brasileiro - JBNEWS</t>
+          <t>Mosaic paralisa produção em Catalão por falta de enxofre e sindicato teme impacto em 650 empregos - Diário de Goiás</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>20/07/2026 13:41</t>
+          <t>20/07/2026 12:29</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQa3FIWUJOeFVabjdUd3VBS2FRV29fQlpNaURDU3ZpdlB2b2UwNnpreFF5aFg1Z3g4TmM0bmRmZkJRNHUyTjg5dFhZLTVDMEE2b3RHdi16aUJnVUpnYVlodEVFRUg0b3lYUFVwU1lNVy1sX1lreVJ4WnRLOG1SODVuUW95ZkZyQm5WOXhPNXF1VTR5S21DVEdJZ3dZWVVETFNESlRBTVZyd1NDNEhXbzN6cXdha2RISVhIVVJSeS1peWNRZlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNend4a0d3ZVRsdjhtTWlXRWhJQTBlSXFEdjNYX1ZpcElMY0FiUzUySmM1dzQ3TmJwOHhYeGF1eE1jYXYyUXhvWVVOUDdoT05keEg3QmFZbHpzZVByVG4zLV9VZnVHNlYyTHhUUTVoVFB2UlNQWHVXNElsV2N1MjRlVUxLNVhadGRucjB4LURtdXJWSHRPem1QYmFDNVVrNXFTMUFuNkdlMVhyU3pLRmFUV2VvYU1YVWpZLTVMY2pHNDlKTTJXTE81YmtfdVlHVDg?oc=5</t>
         </is>
       </c>
     </row>
@@ -1986,149 +1986,149 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mosaic paralisa produção em Catalão por falta de enxofre e sindicato teme impacto em 650 empregos - Diário de Goiás</t>
+          <t>Da guerra no Oriente Médio à Mosaic: entenda por que empregos estão em risco em Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>20/07/2026 12:29</t>
+          <t>20/07/2026 11:24</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNend4a0d3ZVRsdjhtTWlXRWhJQTBlSXFEdjNYX1ZpcElMY0FiUzUySmM1dzQ3TmJwOHhYeGF1eE1jYXYyUXhvWVVOUDdoT05keEg3QmFZbHpzZVByVG4zLV9VZnVHNlYyTHhUUTVoVFB2UlNQWHVXNElsV2N1MjRlVUxLNVhadGRucjB4LURtdXJWSHRPem1QYmFDNVVrNXFTMUFuNkdlMVhyU3pLRmFUV2VvYU1YVWpZLTVMY2pHNDlKTTJXTE81YmtfdVlHVDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbHZvTzRTZHlrTHpsQmFFV0k2Qi0wWTh1SXhHN0pvcDgwUzVHRGFVVzc4bXNSeHJLRGlwQzkzRWxtYVJERFBReVlRaC1paTNIRHN0YWVhc0QxQnJyaXBrdzhqeWdtSzZ6Vk1jaU9SZ0VNMkc3UHg0YlRVdmtFNVZWT0tybTdRUm9STWt4SlBKM0ktLXZ2SVRtb3ZYaC1ZV2VSQ0NqMWoyVmROQUVBNDNyazNmLTFvc3l3M2JzWDlKUHlaUmdM0gHMAUFVX3lxTE1qQkF4YVY1VXNFRjdHSllUaTJOM0c2V3V4Y1dYYWJyWmFDOXlJWXZVaEd1MWxhS185REZyc3owaHA5NjlrSzNSdC0wc3hzOXBkQ2xrMnRPcFZ6ZUFHYXlxcDQ4eUxBSU12Z2luVVNFRVMyRGx6SnJxeXVwQmhKT0FSODNWZVVPekNqVlM4aUVWSE5iTHRiRHl6RklWMkRGTXQzVW5YN1VBS0YtUERfeWlLX3hsNk1nZGJUc3diRTBqZ3ZLWmNjMWpKNWkxQw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Da guerra no Oriente Médio à Mosaic: entenda por que empregos estão em risco em Uberaba - JM Online</t>
+          <t>Cotações Agrícolas para esta Segunda-feira 20 de Julho de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>20/07/2026 11:24</t>
+          <t>20/07/2026 10:55</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbHZvTzRTZHlrTHpsQmFFV0k2Qi0wWTh1SXhHN0pvcDgwUzVHRGFVVzc4bXNSeHJLRGlwQzkzRWxtYVJERFBReVlRaC1paTNIRHN0YWVhc0QxQnJyaXBrdzhqeWdtSzZ6Vk1jaU9SZ0VNMkc3UHg0YlRVdmtFNVZWT0tybTdRUm9STWt4SlBKM0ktLXZ2SVRtb3ZYaC1ZV2VSQ0NqMWoyVmROQUVBNDNyazNmLTFvc3l3M2JzWDlKUHlaUmdM0gHMAUFVX3lxTE1qQkF4YVY1VXNFRjdHSllUaTJOM0c2V3V4Y1dYYWJyWmFDOXlJWXZVaEd1MWxhS185REZyc3owaHA5NjlrSzNSdC0wc3hzOXBkQ2xrMnRPcFZ6ZUFHYXlxcDQ4eUxBSU12Z2luVVNFRVMyRGx6SnJxeXVwQmhKT0FSODNWZVVPekNqVlM4aUVWSE5iTHRiRHl6RklWMkRGTXQzVW5YN1VBS0YtUERfeWlLX3hsNk1nZGJUc3diRTBqZ3ZLWmNjMWpKNWkxQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQTFNselBTQzRUNjBiZlAxdXZBeDVOU3FoVVNZVDUxQU9ING1qbThzNk9rMmZ0elduWnhBOFhYN09IMlpZS0J3WTAyX1ZnN1plTVV2eEVmSDJzZHRkSWh2ZUlEbFVJLVJFaGc4N19CNGdscENfSkc5WHVVNUlTeU4xeVY0c3V0THRkWWVwSEJvcXpHQ3l0emV4M3gwd185QnBTeWJldTNFWjU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Segunda-feira 20 de Julho de 2026 - RRMAIS</t>
+          <t>Galeria de Masonry Stone Walls - Dietfurt Limestone - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>20/07/2026 10:55</t>
+          <t>20/07/2026 10:28</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQTFNselBTQzRUNjBiZlAxdXZBeDVOU3FoVVNZVDUxQU9ING1qbThzNk9rMmZ0elduWnhBOFhYN09IMlpZS0J3WTAyX1ZnN1plTVV2eEVmSDJzZHRkSWh2ZUlEbFVJLVJFaGc4N19CNGdscENfSkc5WHVVNUlTeU4xeVY0c3V0THRkWWVwSEJvcXpHQ3l0emV4M3gwd185QnBTeWJldTNFWjU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPbE80ZEdXckRKM1JJTFh2QTJ1bHpvczcxSXFpTlBjNnB5anhZT1JXaHgzMzVETGFBY05PdEh4QkFua3BrYjRSLWZ3NTJScDd1MXNUYmxjX3lNSC1OdEU5NVIxZDU1Ty1mdmwwR18xQW9nbDFnVVhQeDJmN3N5VkdjenpkWmFWX0FMZ2Qxc3lMeUdpQjJtYndpbnBHT29nYmhobWg4emNOMU5zbllZMXZRWlF5NVU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Galeria de Masonry Stone Walls - Dietfurt Limestone - 4 - ArchDaily</t>
+          <t>Murang'a county distributes lime to coffee farmers to boost production</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>20/07/2026 10:28</t>
+          <t>20/07/2026 03:43</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPbE80ZEdXckRKM1JJTFh2QTJ1bHpvczcxSXFpTlBjNnB5anhZT1JXaHgzMzVETGFBY05PdEh4QkFua3BrYjRSLWZ3NTJScDd1MXNUYmxjX3lNSC1OdEU5NVIxZDU1Ty1mdmwwR18xQW9nbDFnVVhQeDJmN3N5VkdjenpkWmFWX0FMZ2Qxc3lMeUdpQjJtYndpbnBHT29nYmhobWg4emNOMU5zbllZMXZRWlF5NVU?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc56763543d3a4fb9431988bed82&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Murang'a county distributes lime to coffee farmers to boost production</t>
+          <t>Mosaic pode demitir mais 650 trabalhadores em Catalão - O Popular</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>20/07/2026 03:43</t>
+          <t>19/07/2026 22:37</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e8948ec64b329dae15207f41790c&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOWC0wUm16Y1hGUHdCR2JRdnhOT0JyM3UxQ2tlVndJQVhDVWw5cU1WdlNIWnpFdzVpNDlrb294TFB5MERjbnZrZVpOOVMyOUtwRXZVNWJoakRQYlc2Z1lwYV9RaFhBbTZ2WFFnc2E0LTZ4UXg0NlFvVHB4c0JPQ0czam5YdTEwRmlqVnEtUi0tOC1MOFRtaWh1MW9zTHA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mosaic pode demitir mais 650 trabalhadores em Catalão - O Popular</t>
+          <t>Proteína ajusta defesa vegetal à oferta de enxofre - Revista Cultivar</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>19/07/2026 22:37</t>
+          <t>19/07/2026 09:40</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOWC0wUm16Y1hGUHdCR2JRdnhOT0JyM3UxQ2tlVndJQVhDVWw5cU1WdlNIWnpFdzVpNDlrb294TFB5MERjbnZrZVpOOVMyOUtwRXZVNWJoakRQYlc2Z1lwYV9RaFhBbTZ2WFFnc2E0LTZ4UXg0NlFvVHB4c0JPQ0czam5YdTEwRmlqVnEtUi0tOC1MOFRtaWh1MW9zTHA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOVGlUQzZ6UDhYaDg3ZUNHTEwwbDBZcTlnVUVGUTFkalFpLUpQSVRnSTZCOVFYcGlub0FBSWNSTGE2WEFfS0ZpdFNnZGZyU3hick90QmF2WmpIUWNYVVNqajhBVUZSREF3UVJtMzJKT25sVTZkVU1UQzhZR0VENFdMRTVfRU10dTNOSllMdHlraGllX056?oc=5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Proteína ajusta defesa vegetal à oferta de enxofre - Revista Cultivar</t>
+          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>19/07/2026 09:40</t>
+          <t>19/07/2026 04:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOVGlUQzZ6UDhYaDg3ZUNHTEwwbDBZcTlnVUVGUTFkalFpLUpQSVRnSTZCOVFYcGlub0FBSWNSTGE2WEFfS0ZpdFNnZGZyU3hick90QmF2WmpIUWNYVVNqajhBVUZSREF3UVJtMzJKT25sVTZkVU1UQzhZR0VENFdMRTVfRU10dTNOSllMdHlraGllX056?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
         </is>
       </c>
     </row>
@@ -2140,61 +2140,61 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
+          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - Revista Oeste</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>19/07/2026 04:00</t>
+          <t>18/07/2026 04:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - Revista Oeste</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>18/07/2026 04:00</t>
+          <t>18/07/2026 01:44</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
+          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>18/07/2026 01:44</t>
+          <t>17/07/2026 20:47</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
         </is>
       </c>
     </row>
@@ -2206,237 +2206,237 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
+          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>17/07/2026 20:47</t>
+          <t>17/07/2026 20:39</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
+          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>17/07/2026 20:39</t>
+          <t>17/07/2026 10:55</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 12 - ArchDaily</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>17/07/2026 10:55</t>
+          <t>17/07/2026 10:47</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOVG5QeHc1MVllRXpLZGR1REtSVWZxMi12LUdudEh5My1CN3lKc1dCd0U4SFdjWTE1RWF1cUJYbk5ZTEppUkkycm45U3VSRldONnFLV3RONGFTZG5XS2ZWdkIwNjJVeEFLRGdleGU5ZWFoeWpyTzNZN0tCQ2NCM3BJWl9laF9kVG5BcmVVVWp1RnFjOEhXYTNqSFJCN0NJMkxSa09lZldnUHhma052SDAzNlJLSFQ0bkUyUWJGYU1kZHhyemJpd2N4ZlZwcDE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 12 - ArchDaily</t>
+          <t>Galeria de Porcelanato - serie New Limestone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>17/07/2026 10:47</t>
+          <t>17/07/2026 05:20</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOVG5QeHc1MVllRXpLZGR1REtSVWZxMi12LUdudEh5My1CN3lKc1dCd0U4SFdjWTE1RWF1cUJYbk5ZTEppUkkycm45U3VSRldONnFLV3RONGFTZG5XS2ZWdkIwNjJVeEFLRGdleGU5ZWFoeWpyTzNZN0tCQ2NCM3BJWl9laF9kVG5BcmVVVWp1RnFjOEhXYTNqSFJCN0NJMkxSa09lZldnUHhma052SDAzNlJLSFQ0bkUyUWJGYU1kZHhyemJpd2N4ZlZwcDE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUm10el9ibGdzeXJnbUozcmNURExkYmRjNVpSUEdNblBrZE1oQ0Y2TEs4NlNsTGJIVmllNFB2a2FDRDBZM1dxc2I1ZTl0alJIU3dHZXczLUhMYUUwMXhQUWdvbk5LdTFwby1KYzV2aDJMWVhBa3h5bWVxdm8tN19FV3BYOXRhVERCS0I4a3d1SDdtdV9LVlloVHVCYTBvS3o2dXhr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Galeria de Porcelanato - serie New Limestone - 3 - ArchDaily</t>
+          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>17/07/2026 05:20</t>
+          <t>17/07/2026 04:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUm10el9ibGdzeXJnbUozcmNURExkYmRjNVpSUEdNblBrZE1oQ0Y2TEs4NlNsTGJIVmllNFB2a2FDRDBZM1dxc2I1ZTl0alJIU3dHZXczLUhMYUUwMXhQUWdvbk5LdTFwby1KYzV2aDJMWVhBa3h5bWVxdm8tN19FV3BYOXRhVERCS0I4a3d1SDdtdV9LVlloVHVCYTBvS3o2dXhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
+          <t>Galeria de Limestone, Granite and Travertine - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>17/07/2026 04:00</t>
+          <t>17/07/2026 03:58</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOY0pYQ3FwR0g1cHlZMnk3bnlsc1dqRFlqZ3ktVWcycHB5TU9GcDRSOFUweHpsXzA4VzVYdkh0QS1RV2JoYkNLZXB2bzhrQmNPZHVwUnowVERPYTNqLU8zelNPUVZZQU5lLVk2UnJRYlI5Q2wxTVBSLVpKYXQ1NWl2VUh1VDJTQUQ1Nk9EekZUWmk0NGhsLW9hM3FLVmQ4b0lsempwNGl0NzRpWXFpcVpyT2VfVm9nLW1UT2YteklKdlZTQV9zM1RJMTBZcXdhMFppR0NkbGhPSlE1SS13R2VNUFJwcXFnZ3dic192am9xSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Galeria de Limestone, Granite and Travertine - 8 - ArchDaily</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 25 - ArchDaily</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>17/07/2026 03:58</t>
+          <t>17/07/2026 01:18</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOY0pYQ3FwR0g1cHlZMnk3bnlsc1dqRFlqZ3ktVWcycHB5TU9GcDRSOFUweHpsXzA4VzVYdkh0QS1RV2JoYkNLZXB2bzhrQmNPZHVwUnowVERPYTNqLU8zelNPUVZZQU5lLVk2UnJRYlI5Q2wxTVBSLVpKYXQ1NWl2VUh1VDJTQUQ1Nk9EekZUWmk0NGhsLW9hM3FLVmQ4b0lsempwNGl0NzRpWXFpcVpyT2VfVm9nLW1UT2YteklKdlZTQV9zM1RJMTBZcXdhMFppR0NkbGhPSlE1SS13R2VNUFJwcXFnZ3dic192am9xSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQbFY3SFNuUWE1NVB1UW44bFBMd3NZZWtKVlY2SmU2LXRIaEU4cXBEUjF5SlVMN1pyQ3pmbUdlU0VmNUl6STVzUE5JcTJfOVFyNlp2WXJ1ajVsTTl5M3RQclFBTEVDbFZhNXVxN3pRRWh5UVZ2UVBMQjYydnI5aWc1SU1LOVUyWUpBLUgtWHc4VVRxSTV2V256LXVnR2xzb2V0M0ljQ2JoT1dMU2NhamI1anJlREV6aGRQZkFuUFlGY0pXY2VYQjdnVWRQMDJaalVWOVd6X2xpRkk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 25 - ArchDaily</t>
+          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>17/07/2026 01:18</t>
+          <t>16/07/2026 20:53</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQbFY3SFNuUWE1NVB1UW44bFBMd3NZZWtKVlY2SmU2LXRIaEU4cXBEUjF5SlVMN1pyQ3pmbUdlU0VmNUl6STVzUE5JcTJfOVFyNlp2WXJ1ajVsTTl5M3RQclFBTEVDbFZhNXVxN3pRRWh5UVZ2UVBMQjYydnI5aWc1SU1LOVUyWUpBLUgtWHc4VVRxSTV2V256LXVnR2xzb2V0M0ljQ2JoT1dMU2NhamI1anJlREV6aGRQZkFuUFlGY0pXY2VYQjdnVWRQMDJaalVWOVd6X2xpRkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>16/07/2026 20:53</t>
+          <t>16/07/2026 15:34</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
+          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>16/07/2026 15:34</t>
+          <t>16/07/2026 14:06</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
+          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>16/07/2026 14:06</t>
+          <t>16/07/2026 11:16</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
         </is>
       </c>
     </row>
@@ -2448,51 +2448,51 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
+          <t>São José: inscrições abertas para programa de transporte de calcário - PortalR3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>16/07/2026 11:16</t>
+          <t>16/07/2026 07:46</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVG5tTDNLd2owRzFfRWszRVRWNzJXUXd6S0dHdEp4Z1EtLV8xSmhzV0wyaHFKUnduUnZLRVo1UHViSkUyNi1lbU9TWUpXT3d1Q0Jwdjg3eWg4cXVWSXFFR0VZdDZpUnV4RnYwTzRIVW5ielUtdFloRnVHQnpoclVqM29TbnJYYV9lQnRLT3lVcHpxbl9OMkFPWXU2LUF1T0t2Y0I5RHA0SWNjdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>São José: inscrições abertas para programa de transporte de calcário - PortalR3</t>
+          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>16/07/2026 07:46</t>
+          <t>16/07/2026 04:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVG5tTDNLd2owRzFfRWszRVRWNzJXUXd6S0dHdEp4Z1EtLV8xSmhzV0wyaHFKUnduUnZLRVo1UHViSkUyNi1lbU9TWUpXT3d1Q0Jwdjg3eWg4cXVWSXFFR0VZdDZpUnV4RnYwTzRIVW5ielUtdFloRnVHQnpoclVqM29TbnJYYV9lQnRLT3lVcHpxbl9OMkFPWXU2LUF1T0t2Y0I5RHA0SWNjdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
+          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e89386da44158366a5ad78e33eab&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc5544b54a1b9356efc8cfad52e2&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2971,12 +2971,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
+          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2986,19 +2986,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
+          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
+          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Um helicóptero despeja 200 toneladas de calcário por dia sobre lagos da Suécia, faz 162 carregamentos em uma única jornada e tenta neutralizar a chuva ácida que alterou a química da água durante décadas - CPG Click Petróleo e Gás</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - Mais Goiás</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3118,19 +3118,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxPMHBUZUlrOVNEWUdWdW85U1h6YVExN3F4UGhUMDFfaXk1RmRDZ1I2Z3BkaXVwVkNrSzVTdGFvMFNhVk12b3VJajRhRlAwYTJ0QVZPRnI0MTFQeFdybDdBVkFnLUhkS19Oei0yRTJ6bWpxVS0zRUU0Slp3QnZzZG5tZjNJSm9DN25FMTJoTEN2U01oQllxc3MyX1RneGJRVElVeGgxQm9nMHRhVFYzOUlIRDhKcUF5YzJ2dGdQZ0tzR0ZYcUxmUXdsVTFKS3A4RXBvYkczSHV0Zk5ZNW5pbmtLeFpFYTVJeDhzN0JHeHRSQ2hsSk1TZ2JubFVUT0NfN3pTSG40SU85WF9VMEJTYmt5bHdNWW9jTlpHeWhQdzRITUtXV3ltSFoycmttVXRsMGtnSTNTMTEza3E2WXlhUkhtY2dnbzhDUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPM3VPUnViV3c5azFIVjI2U2s1QnJuRm90bXJreE0yS2hJVlJOMlY2bm5GNlBBbHIxc0xSZEU1RzE4d1E5bTYzR3NVMy1mNUtIeklma1RJNWFXcWxBTUYzT3VEUndQb0JidTh3S0R6T01XQ3lOQkptQVVoZ2VxWF9fSDRwTHFoa1pLNVFkTE1paU1UTDBIbnhYcEprNndQVHJVekRHd2ZlanRYM0Zra09LR3VSZmVNdzhPMUFqNWFFRFBjNkFMSzZObXdzQnFYa2V6?oc=5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - Mais Goiás</t>
+          <t>Um helicóptero despeja 200 toneladas de calcário por dia sobre lagos da Suécia, faz 162 carregamentos em uma única jornada e tenta neutralizar a chuva ácida que alterou a química da água durante décadas - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPM3VPUnViV3c5azFIVjI2U2s1QnJuRm90bXJreE0yS2hJVlJOMlY2bm5GNlBBbHIxc0xSZEU1RzE4d1E5bTYzR3NVMy1mNUtIeklma1RJNWFXcWxBTUYzT3VEUndQb0JidTh3S0R6T01XQ3lOQkptQVVoZ2VxWF9fSDRwTHFoa1pLNVFkTE1paU1UTDBIbnhYcEprNndQVHJVekRHd2ZlanRYM0Zra09LR3VSZmVNdzhPMUFqNWFFRFBjNkFMSzZObXdzQnFYa2V6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxPMHBUZUlrOVNEWUdWdW85U1h6YVExN3F4UGhUMDFfaXk1RmRDZ1I2Z3BkaXVwVkNrSzVTdGFvMFNhVk12b3VJajRhRlAwYTJ0QVZPRnI0MTFQeFdybDdBVkFnLUhkS19Oei0yRTJ6bWpxVS0zRUU0Slp3QnZzZG5tZjNJSm9DN25FMTJoTEN2U01oQllxc3MyX1RneGJRVElVeGgxQm9nMHRhVFYzOUlIRDhKcUF5YzJ2dGdQZ0tzR0ZYcUxmUXdsVTFKS3A4RXBvYkczSHV0Zk5ZNW5pbmtLeFpFYTVJeDhzN0JHeHRSQ2hsSk1TZ2JubFVUT0NfN3pTSG40SU85WF9VMEJTYmt5bHdNWW9jTlpHeWhQdzRITUtXV3ltSFoycmttVXRsMGtnSTNTMTEza3E2WXlhUkhtY2dnbzhDUkE?oc=5</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
+          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3250,19 +3250,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
+          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
+          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
+          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
+          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
+          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e89a771f40d5a6b20806709807cc&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc5c0e094766bf22439cbc34bcb6&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
+          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3668,19 +3668,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
+          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,41 +3800,41 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>29/06/2026 04:00</t>
+          <t>30/06/2026 04:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -3917,66 +3917,66 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
+          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>28/06/2026 04:00</t>
+          <t>29/06/2026 04:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>"Mosaic", projeto interativo de Steven Soderbergh, pode mudar a forma como assistimos TV - b9.com.br</t>
+          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>27/06/2026 17:23</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQMkg2VUVFQXg4X1EwaTZZaHF3NEhCVkZFdU1QNF9TRUhZeGdOTTIzVk5temdFSURINS1Ob09SNGJ2bmREQ2Roa1YtczZPc2tCTEFLSzNhRVowZGM5V2FFM2VSMVItTTk2ZlUzNmFCYXFCNjJvdTFIZV80b1hSamdmYTVvWUFQM1U0NkR6RDZ2a2EtUXlBVHFJX2wwYW55TGE2VDhISjdmM1ZjTHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>"Mosaic", projeto interativo de Steven Soderbergh, pode mudar a forma como assistimos TV - b9.com.br</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>27/06/2026 17:23</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQMkg2VUVFQXg4X1EwaTZZaHF3NEhCVkZFdU1QNF9TRUhZeGdOTTIzVk5temdFSURINS1Ob09SNGJ2bmREQ2Roa1YtczZPc2tCTEFLSzNhRVowZGM5V2FFM2VSMVItTTk2ZlUzNmFCYXFCNjJvdTFIZV80b1hSamdmYTVvWUFQM1U0NkR6RDZ2a2EtUXlBVHFJX2wwYW55TGE2VDhISjdmM1ZjTHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4032,51 +4032,51 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>25/06/2026 19:02</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e89cf9bc4070a2bef2d9a6a5f5c0&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f06%2fcom-pouco-enxofre-industria-de-fertilizante-ja-teme-paralisacoes.ghtml&amp;c=5295783801695414575&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CMOC: Produção de cobre, cobalto e nióbio aumenta em relação ao mesmo período do ano anterior no primeiro trimestre; planeja produzir 600.000-660.000 toneladas de cobre metal em 2025 - Shanghai Metals Market</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>25/06/2026 02:45</t>
+          <t>25/06/2026 19:02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNeHdIR1BSb0xPU1ZwbXhzOFpLcm5VUlpxLXhIdU4xLXUxbjZKTlhIMFhGRnJuTFBYejVabTNBNUtyVDZPbVBaeXcySUhGN2YxTDBLdVpfUllHOGdkNjN1SWpWOXBfck54ZVRJVFQyYUh6Yy1QX0ZCN29nQzRhRWxON0d4bjJJU2JQbDAtakZKcGZ1enZzaEVlamgyUnR3WmVpamJwM1JSS0pZS1NiYUU2aXEyc0E2bzhQa0Z6S2ZlWHhMb1BMQVlVb1NMdjFCeHJyRlEwUWNJdTFUdWdMVXcyOWRSaXRmSW9rRldyaGtndkMxSTlPUHVQNS1JamF0X2tDTHc?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc5e596946efa69da00946468f61&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f06%2fcom-pouco-enxofre-industria-de-fertilizante-ja-teme-paralisacoes.ghtml&amp;c=5295783801695414575&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4086,19 +4086,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - portalarauto.com.br</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4108,19 +4108,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - portalarauto.com.br</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
+          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4152,19 +4152,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4174,19 +4174,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - portalarauto.com.br</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4262,19 +4262,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - portalarauto.com.br</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
+          <t>Calcário ganha espaço no campo após alta dos fertilizantes e pode beneficiar produtores do Nordeste - Paraíba Business</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPdHRzWEdaMFMwRjhjQ2w2Z2I0VkNic0xRT2w5dTVkUVpUOWRVRkxFRG1sa3Yxbk80cGlrcWhiVExVVG15M3Npb2FyUU1tekhiSjZiOHV6ZGRqR2NOVzN3MTN1cUQ2SEZqTWI2Y3VGTEM3dVI2dnBHOU5pZ1Q5MVVKX2dueHF1RkoyTVRnamExN1ktcmoybUhtT2Q0WmZqYUZYb2NGaXNMUUtjWXFMdzFqYzhKTWFmZWpvb2YwUlN2TVRValViS1E1RnJtZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4570,19 +4570,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Calcário ganha espaço no campo após alta dos fertilizantes e pode beneficiar produtores do Nordeste - Paraíba Business</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPdHRzWEdaMFMwRjhjQ2w2Z2I0VkNic0xRT2w5dTVkUVpUOWRVRkxFRG1sa3Yxbk80cGlrcWhiVExVVG15M3Npb2FyUU1tekhiSjZiOHV6ZGRqR2NOVzN3MTN1cUQ2SEZqTWI2Y3VGTEM3dVI2dnBHOU5pZ1Q5MVVKX2dueHF1RkoyTVRnamExN1ktcmoybUhtT2Q0WmZqYUZYb2NGaXNMUUtjWXFMdzFqYzhKTWFmZWpvb2YwUlN2TVRValViS1E1RnJtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -4643,12 +4643,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
@@ -4687,12 +4687,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4768,19 +4768,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4819,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - StoneX</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - StoneX</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5032,19 +5032,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5098,19 +5098,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Paraná Central</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdk56ZUFYa2pGdWtqdzRMRjJNTmRzNExlY3pPSnpmZjVsQ2ZCT3pJeDl1UGk1dzR1bmRJYjB0akk5alp1YW83empGWHY2TVhzWXdfRHlrenRSRFNHUmx5dS1pLW83YXhWX3ZsSldMM3luSXNScEJRUUpNdTVBM3hTV2tFdDdnRkZvTkowU3IxbU1ZWTBiNVRKSXRhWi05QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Paraná Central</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdk56ZUFYa2pGdWtqdzRMRjJNTmRzNExlY3pPSnpmZjVsQ2ZCT3pJeDl1UGk1dzR1bmRJYjB0akk5alp1YW83empGWHY2TVhzWXdfRHlrenRSRFNHUmx5dS1pLW83YXhWX3ZsSldMM3luSXNScEJRUUpNdTVBM3hTV2tFdDdnRkZvTkowU3IxbU1ZWTBiNVRKSXRhWi05QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,19 +5252,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -5528,51 +5528,51 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>26/05/2026 04:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>26/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,19 +5582,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5604,19 +5604,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5626,19 +5626,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5670,19 +5670,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5692,63 +5692,63 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>23/05/2026 04:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>23/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5787,12 +5787,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5831,34 +5831,34 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,41 +5868,41 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5912,19 +5912,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5934,19 +5934,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5956,19 +5956,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5978,19 +5978,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6000,41 +6000,41 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6066,63 +6066,63 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Conexão Cultural – Jornada ESG chega a Minas Gerais, Bahia e Maranhão para conscientizar sobre sustentabilidade - O Maranhense</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>18/05/2026 14:18</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUHhsWkkwMlFtdl9jNVN3cXd5YlRZc1kzQVZ1aW02X1pUZFFKUFUyNHZkNVlBZzFfTHo1VmFleU1pU2JNakxXZ083RXNvUzRXY29aS0IyeE45S3FmUlJ2MW1pYVhSRjlhSzRiOGxyNkItU3dtMVNYX3o1RnVQVUc5QUlYdnJhWWVhc0dRVDVCS1cxWllGNGR5R3hLeHZNODJhakRpWjFpNFRIRUxfdFUxMmJYTHdaY1piVHdWc25pb2VRSVR3emd3aG9MQUh1UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Conexão Cultural – Jornada ESG chega a Minas Gerais, Bahia e Maranhão para conscientizar sobre sustentabilidade - O Maranhense</t>
+          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>18/05/2026 14:18</t>
+          <t>18/05/2026 04:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUHhsWkkwMlFtdl9jNVN3cXd5YlRZc1kzQVZ1aW02X1pUZFFKUFUyNHZkNVlBZzFfTHo1VmFleU1pU2JNakxXZ083RXNvUzRXY29aS0IyeE45S3FmUlJ2MW1pYVhSRjlhSzRiOGxyNkItU3dtMVNYX3o1RnVQVUc5QUlYdnJhWWVhc0dRVDVCS1cxWllGNGR5R3hLeHZNODJhakRpWjFpNFRIRUxfdFUxMmJYTHdaY1piVHdWc25pb2VRSVR3emd3aG9MQUh1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>Ureia recua 14% em 4 semanas com demanda global enfraquecida - StoneX</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6132,19 +6132,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOZ0Z5WTFwOXBJc0NMYzFPcGRCWmRzVU1sc3ViLXNJVmJVelhDZE5jNkxZRGJSLU8zb3pUYWVpYWxJVDdLOGpzU0pzSWd5VExmeGF0SVhJLTZsMExmN194V3dONHF5cmdrVGE4WlRETVB4RklMbllPQnRlODctRE1FTlFKRHcyU1h0Tkw2WVYzWTJzN2lDcTNtcEdFdFZGLWgyT1FvdUZOekQzUTNINlAzMjI0TFQtRGtLd3FtQi10N2JUVUc5cGZxNXZSMnZHNUlQd3NVOFhuM0ZzcnF0ZDVN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Ureia recua 14% em 4 semanas com demanda global enfraquecida - StoneX</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOZ0Z5WTFwOXBJc0NMYzFPcGRCWmRzVU1sc3ViLXNJVmJVelhDZE5jNkxZRGJSLU8zb3pUYWVpYWxJVDdLOGpzU0pzSWd5VExmeGF0SVhJLTZsMExmN194V3dONHF5cmdrVGE4WlRETVB4RklMbllPQnRlODctRE1FTlFKRHcyU1h0Tkw2WVYzWTJzN2lDcTNtcEdFdFZGLWgyT1FvdUZOekQzUTNINlAzMjI0TFQtRGtLd3FtQi10N2JUVUc5cGZxNXZSMnZHNUlQd3NVOFhuM0ZzcnF0ZDVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6166,39 +6166,39 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
+          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>17/05/2026 14:07</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>17/05/2026 14:07</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
@@ -6227,44 +6227,44 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>O obstáculo virou o caminho - CNN Brasil</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>14/05/2026 04:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>O obstáculo virou o caminho - CNN Brasil</t>
+          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>14/05/2026 04:00</t>
+          <t>13/05/2026 04:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -6276,17 +6276,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>13/05/2026 04:00</t>
+          <t>12/05/2026 04:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6364,17 +6364,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Secultur</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>11/05/2026 13:42</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6386,17 +6386,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Secultur</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>11/05/2026 13:42</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Portal Arcos</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNM3R6UVBxdkNBVUhSN0twLW5Vc1JrNERWVzF2Z25iM1B0WHlsQXVqdjVqQ195a2lhaU1QeFl6Wm5jSldfOHkzaWlHbDdTTG5KS2xHSEdRMFBRVE9JWldkTlppZHJvRGk1V2RWekVUNTZEcWg2dkRQbVJtVDRjdF9VcXZadnY2Z2lnYzEzUWttRnpKV2dPNi1iZHF4TUtUQTdrVTI4X3c5dUFTZkZHaWIzR0JiQ3JMdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6462,19 +6462,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6535,44 +6535,44 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>10/05/2026 04:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>10/05/2026 04:00</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6623,56 +6623,56 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
+          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>06/05/2026 11:23</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>06/05/2026 11:23</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -6716,17 +6716,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>05/05/2026 04:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6738,29 +6738,29 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>05/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6770,19 +6770,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6836,19 +6836,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,19 +6858,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
@@ -6892,17 +6892,17 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>01/05/2026 04:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6914,29 +6914,29 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>01/05/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Quinta-feira 30 de Abril de 2026 - RRMAIS</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,19 +6946,19 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUXhYaUtDQ3pyNUxlZFV3ZjlIYVFHOTNhV21VN3RPdFNGTUYtSWpURXVnZjlhWHl1cDdfN3phMmNDcmQxejFrVkdqdG96Ymc2YTFwLXlzaUFsZXFKaG5GZ2Z2c3pCMnBuZk14RjVXclZlRmhjbVdfMUFXUEFOVVBNVl81NzdCdlNJQXhPbE01eTJBX1hPRm12dC0ybURMV3YtbG1aUldwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Cotações Agrícolas para esta Quinta-feira 30 de Abril de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUXhYaUtDQ3pyNUxlZFV3ZjlIYVFHOTNhV21VN3RPdFNGTUYtSWpURXVnZjlhWHl1cDdfN3phMmNDcmQxejFrVkdqdG96Ymc2YTFwLXlzaUFsZXFKaG5GZ2Z2c3pCMnBuZk14RjVXclZlRmhjbVdfMUFXUEFOVVBNVl81NzdCdlNJQXhPbE01eTJBX1hPRm12dC0ybURMV3YtbG1aUldwSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7078,19 +7078,19 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,39 +7112,39 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>29/04/2026 04:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
+          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>29/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7166,63 +7166,63 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Mercado de enxofre corto de compressão varre através da cadeia de suprimentos - Sunsirs</t>
+          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQbnRCaEVzdkRzQ0tXZHFVZWd1cmFPVlJxcDc5VDY4bnRxaUx2YmRBdXdLOW9TaEhfWTk1Vmp2SldCZktYcmRfNzRaLVozOE9pZ3p4NEZEdTZXNmk1a2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral News</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,19 +7232,19 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7254,19 +7254,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral News</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,85 +7276,85 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>24/04/2026 04:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>24/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Vereador fiscaliza poda, limpeza e iluminação na rua do Enxofre - camarapiracicaba.sp.gov.br</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7364,19 +7364,19 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPMmlXendqSU95eU95LVd3eFVTZ0lmZTJsZXlmeWpTYnhzcnJMZ0ZMQzdIaGRrOWJGLTY1MlZvT3Y1cURXX0Flb1Y3M1gzR0pKOFpuOG5EbGs2WmZkWTdZQVRKMFFrMmRZeEJIUk81dkRNQm8tX1dkSlZRZ2VQbzJ6enpYb1dTd1NwaXZHdG9FM3JFTWVURG9CRVIxY3hObVNleHJKZ2U4Z1hWRWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Vereador fiscaliza poda, limpeza e iluminação na rua do Enxofre - camarapiracicaba.sp.gov.br</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7386,95 +7386,95 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPMmlXendqSU95eU95LVd3eFVTZ0lmZTJsZXlmeWpTYnhzcnJMZ0ZMQzdIaGRrOWJGLTY1MlZvT3Y1cURXX0Flb1Y3M1gzR0pKOFpuOG5EbGs2WmZkWTdZQVRKMFFrMmRZeEJIUk81dkRNQm8tX1dkSlZRZ2VQbzJ6enpYb1dTd1NwaXZHdG9FM3JFTWVURG9CRVIxY3hObVNleHJKZ2U4Z1hWRWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>21/04/2026 18:42</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQnFTQVFGck1DaWNqWmRkcW1KY3dLTDJRNFRtNlRtREVUdHoyLXZyNWlHS2k1bDlBMzdyQnVOZVhfd2FqUXppTk9BU0Q2azBNcWxGYzlweG5NWVdGR1NpenFnMGdZSDk1QWVtMVdXNllwZElMQWFfZ1Y3R01RWkxSeWJPelZGSkg3dTlNUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>21/04/2026 18:42</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
+          <t>Fertilizantes: energia para o​​ campo - Petrobras</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>18/04/2026 16:01</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQnFTQVFGck1DaWNqWmRkcW1KY3dLTDJRNFRtNlRtREVUdHoyLXZyNWlHS2k1bDlBMzdyQnVOZVhfd2FqUXppTk9BU0Q2azBNcWxGYzlweG5NWVdGR1NpenFnMGdZSDk1QWVtMVdXNllwZElMQWFfZ1Y3R01RWkxSeWJPelZGSkg3dTlNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBFN2xBdUVqSm45WFdPbHdxWWNPY3lEUW0yN01OeThJMGxoYVhCU3Vfa2pJYXItMzN5NjFOS2IyTEd0OUM0LVZoSV9Oa1VBbG5DSlp6Q3VpNEtyWWFHTVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7486,61 +7486,61 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>17/04/2026 04:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Fertilizantes: energia para o​​ campo - Petrobras</t>
+          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>18/04/2026 16:01</t>
+          <t>15/04/2026 19:32</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBFN2xBdUVqSm45WFdPbHdxWWNPY3lEUW0yN01OeThJMGxoYVhCU3Vfa2pJYXItMzN5NjFOS2IyTEd0OUM0LVZoSV9Oa1VBbG5DSlp6Q3VpNEtyWWFHTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>17/04/2026 04:00</t>
+          <t>14/04/2026 04:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7552,51 +7552,51 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>15/04/2026 19:32</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>14/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>CSN apresenta inovação sustentável no Vale do Café - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7606,51 +7606,51 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQW5tN1NZako4UHpaYzVCYklISkM1ZWZxWEJNazdiTmdSdi1aWVBFZXV3bTQxeDZlTHljTWNiblhsUzQ0LWplMTFnU2lCak90d1dLbXRRM1lBZ2xMUGJOUzAyeEFiendSRXI0cFVYMWlZMTZXVXBtZE5VWlJqSFpVbF82S2dKdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>CSN apresenta inovação sustentável no Vale do Café - A Voz da Cidade</t>
+          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQW5tN1NZako4UHpaYzVCYklISkM1ZWZxWEJNazdiTmdSdi1aWVBFZXV3bTQxeDZlTHljTWNiblhsUzQ0LWplMTFnU2lCak90d1dLbXRRM1lBZ2xMUGJOUzAyeEFiendSRXI0cFVYMWlZMTZXVXBtZE5VWlJqSFpVbF82S2dKdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7679,44 +7679,44 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7728,17 +7728,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7750,17 +7750,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7782,19 +7782,19 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Copa do Calcário 2026 inicia em abril com sete clubes da Região Centro-Norte - Jornal O Fluminense</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTFV2aE9QamdoTlhzd051c1VfLWpKQTdQcnNoM250c0dZd0VUd2NTMG5MWW1laWY3N2hEVkp4cUNNelJDam1WWFZOMHVrNUdONzVFVlZrNS1CaHBSVmNwV1Q2QmxyM0tqVnF3MmhDLTA0ajJXeGUyRUN0WlQ1dU9CeVZPTHl5WkdHN2xSVDBfdXo5Z2dFaUN5UnY4RFN4clpkU2taZ2hDOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7826,19 +7826,19 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7892,19 +7892,19 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7914,41 +7914,41 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 inicia em abril com sete clubes da Região Centro-Norte - Jornal O Fluminense</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTFV2aE9QamdoTlhzd051c1VfLWpKQTdQcnNoM250c0dZd0VUd2NTMG5MWW1laWY3N2hEVkp4cUNNelJDam1WWFZOMHVrNUdONzVFVlZrNS1CaHBSVmNwV1Q2QmxyM0tqVnF3MmhDLTA0ajJXeGUyRUN0WlQ1dU9CeVZPTHl5WkdHN2xSVDBfdXo5Z2dFaUN5UnY4RFN4clpkU2taZ2hDOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7970,17 +7970,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8009,44 +8009,44 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>02/04/2026 17:10</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>02/04/2026 17:10</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -8075,22 +8075,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8119,56 +8119,56 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>30/03/2026 04:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
+          <t>Após anos de reclamações por barulho, pequena comunidade rural dos EUA força saída de mineradora de Bitcoin da região - Livecoins</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>30/03/2026 04:00</t>
+          <t>27/03/2026 04:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPcnZsLVNQY3dYX3dtUG5pbkhwZzRTZVFhU0Q1dDEyWllPWjdsc0JKdG9VTkpRd19uOU5lYVpob1kxWS1MMVp6Xzg3VkZpYjJ1UTJ0QXBGRFZxVHY2aTFFQzVRc05SX2ZuSnFjeXdqU2dXYVlDYkNMS0hDRE9iVnBXYUsteTlKTnZYWmwyZXhtMklYVk9JZW1YQ3JPZzNlV054TkFzbnRxaTZqd0Z2dm9XbTRtakRKMXZyQVUtaXlQaTJoVFNiZjlpTFhIQmNwVnVoeDV2elFiTmFnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Após anos de reclamações por barulho, pequena comunidade rural dos EUA força saída de mineradora de Bitcoin da região - Livecoins</t>
+          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8178,29 +8178,29 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPcnZsLVNQY3dYX3dtUG5pbkhwZzRTZVFhU0Q1dDEyWllPWjdsc0JKdG9VTkpRd19uOU5lYVpob1kxWS1MMVp6Xzg3VkZpYjJ1UTJ0QXBGRFZxVHY2aTFFQzVRc05SX2ZuSnFjeXdqU2dXYVlDYkNMS0hDRE9iVnBXYUsteTlKTnZYWmwyZXhtMklYVk9JZW1YQ3JPZzNlV054TkFzbnRxaTZqd0Z2dm9XbTRtakRKMXZyQVUtaXlQaTJoVFNiZjlpTFhIQmNwVnVoeDV2elFiTmFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
+          <t>Corretivo de solo sustentável entra no RenovaBio e gera Créditos de Descarbonização - JornalCana</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>27/03/2026 04:00</t>
+          <t>26/03/2026 04:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQZHNpQzdqYTdMVEl3Tm9xS0R5ZlpYbEpTeFF3ckdFVElTRkZFcGVIVUkwZzQwZC1fenEyVzJLekY2cmNJQmNpMTcwTnRDdjNhQVdHQ0lxZGM2VTdQTmNiOUZGWC1UeGI2S29JeFF2cGR5QWF5Q1dqZFd4S2pucU9fUWMyUVAyMkFRLVhkQkJBZnRRNnpGLUpyVzBOX1FJeHhqTTh1U1pER0YycjZ6VzJId0VqQW93ellCUnJjQnlJWTlPMnZTVzBILUJiME9iaWVScUVDYg?oc=5</t>
         </is>
       </c>
     </row>
@@ -8212,17 +8212,17 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra no RenovaBio e gera Créditos de Descarbonização - JornalCana</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>26/03/2026 04:00</t>
+          <t>25/03/2026 08:19</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQZHNpQzdqYTdMVEl3Tm9xS0R5ZlpYbEpTeFF3ckdFVElTRkZFcGVIVUkwZzQwZC1fenEyVzJLekY2cmNJQmNpMTcwTnRDdjNhQVdHQ0lxZGM2VTdQTmNiOUZGWC1UeGI2S29JeFF2cGR5QWF5Q1dqZFd4S2pucU9fUWMyUVAyMkFRLVhkQkJBZnRRNnpGLUpyVzBOX1FJeHhqTTh1U1pER0YycjZ6VzJId0VqQW93ellCUnJjQnlJWTlPMnZTVzBILUJiME9iaWVScUVDYg?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc5544b54a1b9356efc8cfad52e2&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -8234,29 +8234,29 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>25/03/2026 08:19</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e89386da44158366a5ad78e33eab&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8295,44 +8295,44 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>23/03/2026 04:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>23/03/2026 04:00</t>
+          <t>21/03/2026 04:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
         </is>
       </c>
     </row>
@@ -8344,17 +8344,17 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>21/03/2026 04:00</t>
+          <t>20/03/2026 18:35</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
         </is>
       </c>
     </row>
@@ -8366,51 +8366,51 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
+          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>20/03/2026 18:35</t>
+          <t>20/03/2026 14:42</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
+          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>20/03/2026 14:42</t>
+          <t>20/03/2026 04:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>20/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8486,19 +8486,19 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8508,19 +8508,19 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8530,19 +8530,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8564,39 +8564,39 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
+          <t>Calcário para uso agrícola deve ficar mais barato - Senado</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>18/03/2026 04:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Calcário para uso agrícola deve ficar mais barato - Senado</t>
+          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>18/03/2026 04:00</t>
+          <t>17/03/2026 04:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8608,17 +8608,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
+          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>17/03/2026 04:00</t>
+          <t>16/03/2026 04:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8647,56 +8647,56 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
+          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - portalarauto.com.br</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>16/03/2026 04:00</t>
+          <t>14/03/2026 04:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - portalarauto.com.br</t>
+          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>14/03/2026 04:00</t>
+          <t>13/03/2026 04:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
+          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -8706,51 +8706,51 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
+          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>13/03/2026 04:00</t>
+          <t>12/03/2026 04:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>12/03/2026 04:00</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8779,12 +8779,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
+          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
+          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8816,19 +8816,19 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -8838,63 +8838,63 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
+          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>10/03/2026 12:14</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>10/03/2026 12:14</t>
+          <t>09/03/2026 04:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8904,41 +8904,41 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>09/03/2026 04:00</t>
+          <t>06/03/2026 05:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
+          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -8948,19 +8948,19 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
         </is>
       </c>
     </row>
@@ -8982,51 +8982,51 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
+          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>06/03/2026 05:00</t>
+          <t>05/03/2026 05:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>05/03/2026 05:00</t>
+          <t>04/03/2026 05:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
@@ -9092,29 +9092,29 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9136,83 +9136,83 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>27/02/2026 05:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>27/02/2026 05:00</t>
+          <t>26/02/2026 05:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>26/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - Nativa News</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - Nativa News</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9278,19 +9278,19 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -9300,73 +9300,73 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>19/02/2026 05:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>19/02/2026 05:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Grolime brings high-performance benefits for Scottish soils</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>14/02/2026 06:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e8948ec64b329dae15207f41790c&amp;url=https%3a%2f%2fwww.thescottishfarmer.co.uk%2fnews%2f25845962.grolime-brings-high-performance-benefits-scottish-soils%2f&amp;c=18200927900201231641&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
@@ -9378,39 +9378,39 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9422,83 +9422,83 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
+          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
+          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
+          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9510,17 +9510,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
         </is>
       </c>
     </row>
@@ -9532,39 +9532,39 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
+          <t>China vai investir quase US$ 1 bilhão para assumir minas de ouro no Brasil, controlar milhões de onças do metal e reforçar sua posição global no setor de mineração estratégica - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>02/02/2026 05:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQMkQtMmxTWjZWVEdwcmZYell3OU1VRTl6Z1BTS012WVV3UndnYnZMZ0dLR3pIeElIUndoTlhXLTlQUTVIQnVzcTc4UTgtcm1HSmtjWnhOVkxJdktFSS15dm9jSXpJR19zd1RhcTVzV2ljV21mMnYyMzNoWngyTkt2RmRKN1doQmFEZDAya3BYQ0VOYkN3d01UZkZET3dKWFFSNTdZMEI0bG80Z0pLMXpyWWtQR0ktUG5ab2pISlZVWFhGWVA0cV84RUR6R051Uno1WVd2RVdmQmdiSEhpZ25HQmJjMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
+          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>01/02/2026 05:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9576,39 +9576,39 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>China vai investir quase US$ 1 bilhão para assumir minas de ouro no Brasil, controlar milhões de onças do metal e reforçar sua posição global no setor de mineração estratégica - CPG Click Petróleo e Gás</t>
+          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>02/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQMkQtMmxTWjZWVEdwcmZYell3OU1VRTl6Z1BTS012WVV3UndnYnZMZ0dLR3pIeElIUndoTlhXLTlQUTVIQnVzcTc4UTgtcm1HSmtjWnhOVkxJdktFSS15dm9jSXpJR19zd1RhcTVzV2ljV21mMnYyMzNoWngyTkt2RmRKN1doQmFEZDAya3BYQ0VOYkN3d01UZkZET3dKWFFSNTdZMEI0bG80Z0pLMXpyWWtQR0ktUG5ab2pISlZVWFhGWVA0cV84RUR6R051Uno1WVd2RVdmQmdiSEhpZ25HQmJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
+          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>01/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
         </is>
       </c>
     </row>
@@ -9637,22 +9637,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
+          <t>Ricaços do ouro vendem minas no Brasil por R$ 5,36 bilhões - A Crítica</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>28/01/2026 05:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPMmFvSnQ5bmpvS0ctdmh4VVZSaEFBb1ZfdGZ0TmxvX3htb0dMZTItdmVNVl9VX0tZRTJVb1RLVV9oQjNWZUg1cXBWTmxEWE1zamNwbF9OeWJFeHVLaTdWdnByNUc0QVpray1TUTFXWjdFamFYZzg0MGZnMXA1Qk1ublVQUUtWT2dzZHBHamsxYm9TQ2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -9664,39 +9664,39 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
+          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>27/01/2026 05:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Ricaços do ouro vendem minas no Brasil por R$ 5,36 bilhões - A Crítica</t>
+          <t>Agricultores de Rio Preto da Eva recebem 6 toneladas de calcário - Amazonas1</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>28/01/2026 05:00</t>
+          <t>25/01/2026 05:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPMmFvSnQ5bmpvS0ctdmh4VVZSaEFBb1ZfdGZ0TmxvX3htb0dMZTItdmVNVl9VX0tZRTJVb1RLVV9oQjNWZUg1cXBWTmxEWE1zamNwbF9OeWJFeHVLaTdWdnByNUc0QVpray1TUTFXWjdFamFYZzg0MGZnMXA1Qk1ublVQUUtWT2dzZHBHamsxYm9TQ2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPUGFSbXJwbzhHMGZTUlM2Q3FIWDlpTExxVUJ2SVB0QlZxQU5laGF1WC1DZ3hpZEt6QnVqX2hvWGZuMC1XZ0dOcHcybkVjaWlyWlBCTkJNREpZX1RpRDZDTV9LRlhIZUV2Ry1pckNHTXM3anVuMU02UHg5QVN6NG4tOWlZU3UxU1VBVV80SEVVMTVsZEcz?oc=5</t>
         </is>
       </c>
     </row>
@@ -9708,447 +9708,447 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
+          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>27/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Agricultores de Rio Preto da Eva recebem 6 toneladas de calcário - Amazonas1</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>25/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPUGFSbXJwbzhHMGZTUlM2Q3FIWDlpTExxVUJ2SVB0QlZxQU5laGF1WC1DZ3hpZEt6QnVqX2hvWGZuMC1XZ0dOcHcybkVjaWlyWlBCTkJNREpZX1RpRDZDTV9LRlhIZUV2Ry1pckNHTXM3anVuMU02UHg5QVN6NG4tOWlZU3UxU1VBVV80SEVVMTVsZEcz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>Passa Sete abre inscrições para pedidos de calcário - radiosobradinho.com.br</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>15/01/2026 05:00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQkVmeU43d3FMWjBLMTZ1SWJnVFZSVXFmT3JmM2dFOTdkeFkxLVNodG1ub3hvWEs2eHR4Z3NMd2c5VkFVU2t0S25XYVVEWXRtTHVkUmdVOFdQVGZ3OGJ3YkNmY2xMeGRyLWgxbktJXzhOUF9uN0FWUUcxSnk2cUtFRk5JQ1NHSXJJRHlwcE9oQUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
+          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>14/01/2026 05:00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Tensão no Irã gera incerteza no mercado de ureia - Agrolink</t>
+          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>15/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONkdHa0VwT2VKZExwWll5QlRHbEJoWW4zOW1HRE12cF9ZUTRvTUhodXA1dWlRRGd1Vy1uVC00TS15YkVXU0MyWGs0aGMxdERmdW1KamFNWGZuZTZXUnJqRUFYRVFqN3hXVS1xNllzQ0l1WEdsbnlWV09QOXF0NFpSU3VibVlBV1BpS0gwWld3QXNBX3ZPb3gtTmduZ2VOZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Passa Sete abre inscrições para pedidos de calcário - radiosobradinho.com.br</t>
+          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>15/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQkVmeU43d3FMWjBLMTZ1SWJnVFZSVXFmT3JmM2dFOTdkeFkxLVNodG1ub3hvWEs2eHR4Z3NMd2c5VkFVU2t0S25XYVVEWXRtTHVkUmdVOFdQVGZ3OGJ3YkNmY2xMeGRyLWgxbktJXzhOUF9uN0FWUUcxSnk2cUtFRk5JQ1NHSXJJRHlwcE9oQUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
+          <t>O desafio de produzir com inovação no Brasil - Estadão</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>14/01/2026 05:00</t>
+          <t>12/01/2026 05:00</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOX3RvMHdST1hBVXgyWVRxcHlrcUlvaVBYSVN6M3dfN1h5NGRNWlJYWWh0N0ROcWdrdGQzQlJfNlc1NTNSanAzdlZtTl9sWURGX0FVX1czcGUzVXZxTGJaLUoxNEdFWjVxUVFYcFd1Wjk5QnBteE9ZYUtaMmhJZkxWa0xxUUFyMFNGdGJTOGxNUXJjUlU0ZXlsVXV4VElEdmk0TDFR0gGoAUFVX3lxTE41QUQtbkk2akotTlRCaVJzUDFFUmFYSlZzV0ZQZTFyVExucy14d3hQOHJ1SWZVRGU1cDEyV2ItR0NneExKLWJUWUVYdGpRS0JscWYxOTF1VTV1TV9BMzVUdTFrR0dHSG9iSWdZSGQ0R3VQbG05TzhZZVNJNTFXeU1GeXByNkZ2UEhMdG5WcWlqaGJKZGlFaGV1eXVVZnNydTBrQXlVZHlBcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
+          <t>Sibelco Portugal distinguida a nível nacional e internacional - O Mirante</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>11/01/2026 05:00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPVl8tSExZS016cjFOUVA5NVhOYTlEQk1rZ2xPYldkczhvbHZEUlJScWJJTnhDVkVZeF9tWmZEa2lSbWRfdWRyRHh3aVRzZmlvSE1MRmdVSTRhM2JlakFzWUhFbUQyZnRHbUFPRVZUYS1yTjNnS3RTZFNwWmVkeTlOX0tJZXFOT3F2WFh3OVFCNUNRZ2diSG5BNUtxOE1zOWhpbkJhNXJmdXk3Ykd2aW1J?oc=5</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
+          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>07/01/2026 05:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>O desafio de produzir com inovação no Brasil - Estadão</t>
+          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>12/01/2026 05:00</t>
+          <t>06/01/2026 05:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOX3RvMHdST1hBVXgyWVRxcHlrcUlvaVBYSVN6M3dfN1h5NGRNWlJYWWh0N0ROcWdrdGQzQlJfNlc1NTNSanAzdlZtTl9sWURGX0FVX1czcGUzVXZxTGJaLUoxNEdFWjVxUVFYcFd1Wjk5QnBteE9ZYUtaMmhJZkxWa0xxUUFyMFNGdGJTOGxNUXJjUlU0ZXlsVXV4VElEdmk0TDFR0gGoAUFVX3lxTE41QUQtbkk2akotTlRCaVJzUDFFUmFYSlZzV0ZQZTFyVExucy14d3hQOHJ1SWZVRGU1cDEyV2ItR0NneExKLWJUWUVYdGpRS0JscWYxOTF1VTV1TV9BMzVUdTFrR0dHSG9iSWdZSGQ0R3VQbG05TzhZZVNJNTFXeU1GeXByNkZ2UEhMdG5WcWlqaGJKZGlFaGV1eXVVZnNydTBrQXlVZHlBcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Sibelco</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Sibelco Portugal distinguida a nível nacional e internacional - O Mirante</t>
+          <t>Nova gasolina reduzirá emissão de enxofre em 94% - TN Petróleo</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>11/01/2026 05:00</t>
+          <t>01/01/2026 05:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPVl8tSExZS016cjFOUVA5NVhOYTlEQk1rZ2xPYldkczhvbHZEUlJScWJJTnhDVkVZeF9tWmZEa2lSbWRfdWRyRHh3aVRzZmlvSE1MRmdVSTRhM2JlakFzWUhFbUQyZnRHbUFPRVZUYS1yTjNnS3RTZFNwWmVkeTlOX0tJZXFOT3F2WFh3OVFCNUNRZ2diSG5BNUtxOE1zOWhpbkJhNXJmdXk3Ykd2aW1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPdGFtUGpzV2twUkdYcHRPM2hnZGZUZ2RqUVpLeGtUOGlmbGpkcC1mZUZBOVFoODNSVFNHblFZM2p1UWpwTzFOSjdudEx1RndCUTRMM2FaQlJ2eHBIWmRIbW5qel9JcVlxTEp1ckpPRGdEaDJaU3c4MUVDVHZNNEYtMnVyWkJpakFVbEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
+          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>07/01/2026 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
+          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>06/01/2026 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Nova gasolina reduzirá emissão de enxofre em 94% - TN Petróleo</t>
+          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - MEON</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>01/01/2026 05:00</t>
+          <t>22/12/2025 05:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPdGFtUGpzV2twUkdYcHRPM2hnZGZUZ2RqUVpLeGtUOGlmbGpkcC1mZUZBOVFoODNSVFNHblFZM2p1UWpwTzFOSjdudEx1RndCUTRMM2FaQlJ2eHBIWmRIbW5qel9JcVlxTEp1ckpPRGdEaDJaU3c4MUVDVHZNNEYtMnVyWkJpakFVbEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRnFCa2dQWTktSUZxQW1BRnVBdzhNSkxZUWtlUFVjUWFUTWhMU045UTZWcTJTQ2hneE9wQ1NaU0t4ZFE5MHNVN3dMNWh3NlF1UW1RN0lDVDFfSzZmQlpuMWhfdG1sQ19wWmdweGFaWDNOSHFhTnB3aEo1dXBpRmhTWGF1NE9RaVdSY3ozaTdYbjAyUndhVzZEX3ZJNXJyTlVjazJWRkpVcXVDQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
+          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>20/12/2025 05:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
+          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>19/12/2025 05:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - MEON</t>
+          <t>Preço do enxofre deixa mercado de fertilizantes em alerta - AgFeed</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>22/12/2025 05:00</t>
+          <t>18/12/2025 05:00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRnFCa2dQWTktSUZxQW1BRnVBdzhNSkxZUWtlUFVjUWFUTWhMU045UTZWcTJTQ2hneE9wQ1NaU0t4ZFE5MHNVN3dMNWh3NlF1UW1RN0lDVDFfSzZmQlpuMWhfdG1sQ19wWmdweGFaWDNOSHFhTnB3aEo1dXBpRmhTWGF1NE9RaVdSY3ozaTdYbjAyUndhVzZEX3ZJNXJyTlVjazJWRkpVcXVDQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNdnJJMlZsR3lYS3FUU0JGenh2VHBURDlOaGFlMTFOaHMzSzVwd0RaN2pPQkhpMGJtM1lFZm1kODU1RXFXcWVkV09uZ1ZtRzlKd0VwOF9RcFl0MW9aNERPU05PVWlxMlRvY1dyMFVfemIySDRPOVotS1pqTmE5WGhNNFB4WTBVeWF1SHh6cUVnODduQ0w2NWplM0paWDFpdXA0cXo3MW1NWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
+          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>20/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>19/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Preço do enxofre deixa mercado de fertilizantes em alerta - AgFeed</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>18/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNdnJJMlZsR3lYS3FUU0JGenh2VHBURDlOaGFlMTFOaHMzSzVwd0RaN2pPQkhpMGJtM1lFZm1kODU1RXFXcWVkV09uZ1ZtRzlKd0VwOF9RcFl0MW9aNERPU05PVWlxMlRvY1dyMFVfemIySDRPOVotS1pqTmE5WGhNNFB4WTBVeWF1SHh6cUVnODduQ0w2NWplM0paWDFpdXA0cXo3MW1NWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -10202,29 +10202,29 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10236,17 +10236,17 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10258,29 +10258,29 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10334,29 +10334,29 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - china2brazil.com.br</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,39 +10368,39 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Mineradora chinesa compra minas de ouro no Brasil por US$ 1 bi - Poder360</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUE5hQ3pzUmR2cE5qdjZTUEFxQWVUOXpPTDlLLVNLSVZVR3hmVXVFUG0yLVpRZUN1MHRCMHAxUDRsUm5peUhTSmRsYTdUZnlzNkdEWXdhMHU1ZUFRNTIzNGtXakFfWGo0VFl6OEU3dTdrMXBXQUMxbWM0Ry1CWmJhYV85YlZLSmZmazVjVV8yT2F6NkpIUlEzaHpqSDZycExZd2VhVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - broadcast.com.br</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPY21WSmFRbjB2aU1QUUlkbGgtdW5SUUIyeFhabGpTclNfSHdKbmFGQlJueFY5dU43bzY1R0NtVU5ObkhiTU9jRm1kakNPa0dIOWhsekRnV0VlSnpYLUJCaVNHOXduUDI0enpQczROeVViZGQ1X2kzLWpxMnZiXzh5Q1NSNHJnQ2dSOTlacTZXcjVaOVZSS3hXRTFPbzRzeDBsRFFSM2FERVpLVktSWnVZeTBKbU5DQkNoXy1mRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - china2brazil.com.br</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Mineradora chinesa compra minas de ouro no Brasil por US$ 1 bi - Poder360</t>
+          <t>Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - broadcast.com.br</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUE5hQ3pzUmR2cE5qdjZTUEFxQWVUOXpPTDlLLVNLSVZVR3hmVXVFUG0yLVpRZUN1MHRCMHAxUDRsUm5peUhTSmRsYTdUZnlzNkdEWXdhMHU1ZUFRNTIzNGtXakFfWGo0VFl6OEU3dTdrMXBXQUMxbWM0Ry1CWmJhYV85YlZLSmZmazVjVV8yT2F6NkpIUlEzaHpqSDZycExZd2VhVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPY21WSmFRbjB2aU1QUUlkbGgtdW5SUUIyeFhabGpTclNfSHdKbmFGQlJueFY5dU43bzY1R0NtVU5ObkhiTU9jRm1kakNPa0dIOWhsekRnV0VlSnpYLUJCaVNHOXduUDI0enpQczROeVViZGQ1X2kzLWpxMnZiXzh5Q1NSNHJnQ2dSOTlacTZXcjVaOVZSS3hXRTFPbzRzeDBsRFFSM2FERVpLVktSWnVZeTBKbU5DQkNoXy1mRw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10632,17 +10632,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10654,17 +10654,17 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10676,259 +10676,259 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>12/12/2025 05:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>07/12/2025 19:00</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc56763543d3a4fb9431988bed82&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>Parabenos e dióxido de enxofre fazem mal à saúde? Conheça esses conservantes - Olhar Digital</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>05/12/2025 05:00</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNdWF2bGw2UWZLUTRmVzV4TE1UYlVkQjl6Q1NQMFZ6VVBsZzBMYUk0aWhfYmp2czBONHFCejlJeFVfNGVQQ3RDd2JuTUhJdFFPbHgzSV8tRU9BZTk2aS1ncFZDOUhBZkV4TGh0ZmthdnVjRnFwQng5VGhUQW9MZENYVG9ReDBGTC1IS0VtZkhCaS02VG5wV21UQ2xvc2xva1NHQWh6M1M5cG5CZHk3UkFXMjNpdllxeVQ4TW84bHFWcWhUMzlOR0tOckRua0w?oc=5</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - IBRAM - Mineração do Brasil</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>12/12/2025 05:00</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
+          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>07/12/2025 19:00</t>
+          <t>01/12/2025 05:00</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e8948ec64b329dae15207f41790c&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Parabenos e dióxido de enxofre fazem mal à saúde? Conheça esses conservantes - Olhar Digital</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>05/12/2025 05:00</t>
+          <t>26/11/2025 03:44</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNdWF2bGw2UWZLUTRmVzV4TE1UYlVkQjl6Q1NQMFZ6VVBsZzBMYUk0aWhfYmp2czBONHFCejlJeFVfNGVQQ3RDd2JuTUhJdFFPbHgzSV8tRU9BZTk2aS1ncFZDOUhBZkV4TGh0ZmthdnVjRnFwQng5VGhUQW9MZENYVG9ReDBGTC1IS0VtZkhCaS02VG5wV21UQ2xvc2xva1NHQWh6M1M5cG5CZHk3UkFXMjNpdllxeVQ4TW84bHFWcWhUMzlOR0tOckRua0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>24/11/2025 05:00</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>01/12/2025 05:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>26/11/2025 03:44</t>
+          <t>17/11/2025 13:00</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc5544b54a1b9356efc8cfad52e2&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>24/11/2025 05:00</t>
+          <t>17/11/2025 05:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>11/11/2025 05:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>17/11/2025 13:00</t>
+          <t>10/11/2025 05:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e89386da44158366a5ad78e33eab&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10940,149 +10940,149 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
+          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>17/11/2025 05:00</t>
+          <t>08/11/2025 05:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
+          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>11/11/2025 05:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>10/11/2025 05:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
+          <t>Alta explosiva: preço do enxofre dispara 115% e ameaça elevar custos da agricultura - CompreRural</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>08/11/2025 05:00</t>
+          <t>29/10/2025 04:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOaVRLcmRCTmtsX0FhdlRBTDJXVXpacVE1a1pOdi1yTlBPSlg1TndpelpzMjBIeTFseEd5MjU2ZWdCRVNNVUZleWtDRjVaUnZxRVUzZkN2bjhaZENsSU1ZSktHNlMzaDF0YTNOY0VmdnYyUllnWFVJVWJSaUVFVmQ0VnRZUFRDQ2thRVFLaEhpcXNlWWp4ZGF2WWJNbTI3d0xpQjFUdE5KTEw5a09XN2Rv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>27/10/2025 04:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
+          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>22/10/2025 10:56</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc56763543d3a4fb9431988bed82&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Alta explosiva: preço do enxofre dispara 115% e ameaça elevar custos da agricultura - CompreRural</t>
+          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>29/10/2025 04:00</t>
+          <t>14/10/2025 04:00</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOaVRLcmRCTmtsX0FhdlRBTDJXVXpacVE1a1pOdi1yTlBPSlg1TndpelpzMjBIeTFseEd5MjU2ZWdCRVNNVUZleWtDRjVaUnZxRVUzZkN2bjhaZENsSU1ZSktHNlMzaDF0YTNOY0VmdnYyUllnWFVJVWJSaUVFVmQ0VnRZUFRDQ2thRVFLaEhpcXNlWWp4ZGF2WWJNbTI3d0xpQjFUdE5KTEw5a09XN2Rv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -11094,17 +11094,17 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
+          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - Mundo do Marketing</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>27/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
         </is>
       </c>
     </row>
@@ -11116,369 +11116,369 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
+          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>14/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>10/10/2025 04:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - Mundo do Marketing</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>10/10/2025 04:00</t>
+          <t>02/10/2025 04:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
+          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>02/10/2025 04:00</t>
+          <t>21/09/2025 04:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>20/09/2025 04:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>21/09/2025 04:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>20/09/2025 04:00</t>
+          <t>07/09/2025 14:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc5544b54a1b9356efc8cfad52e2&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>02/09/2025 14:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc5544b54a1b9356efc8cfad52e2&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>07/09/2025 14:00</t>
+          <t>02/09/2025 04:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e89386da44158366a5ad78e33eab&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e89386da44158366a5ad78e33eab&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>22/08/2025 04:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>18/08/2025 14:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68fc56763543d3a4fb9431988bed82&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
+          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>18/08/2025 14:00</t>
+          <t>15/08/2025 04:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a68e8948ec64b329dae15207f41790c&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
+          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>15/08/2025 04:00</t>
+          <t>13/08/2025 04:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
         </is>
       </c>
     </row>
@@ -11507,12 +11507,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
+          <t>Calcário líquido realmente funciona na correção do solo? Confira a explicação - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPb2J3cEFTQUtPejJTNHduUklMXzFHX0NnM09wcmZ6cjR0a1BLTWxlWF9xMGZGNmgyS0RWcTZiZ1ZCOWw2YVZyb1F1bnFWdkYzSEhLa2hzRWN1SXpJZE1tX08tc3BfUERfaFF5SWZhb3RSOEt0eFkyN2ViYVFmZXJOX3UybkNubWZGVmZmazg5S0JBNzJPMlNLeTEtaXdmREdyQjV4dWxJN0NxXy12X1d6UXo0a3F6c3E2SzRXVENmOEJSMDNFaU4wVjBRcUJlYkVROG0xeE5XVUpMVDJH?oc=5</t>
         </is>
       </c>
     </row>
